--- a/Nilai PTS dan ASAS Ganjil 2025-2026/Olah Nilai ASAS/X ASAS/X-1 ASAS INFORMATIKA (Jawaban).xlsx
+++ b/Nilai PTS dan ASAS Ganjil 2025-2026/Olah Nilai ASAS/X ASAS/X-1 ASAS INFORMATIKA (Jawaban).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21750" windowHeight="11950"/>
+    <workbookView windowWidth="14340" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -712,7 +712,7 @@
     <numFmt numFmtId="178" formatCode="m/d/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="179" formatCode="0&quot; / 30&quot;"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -726,6 +726,12 @@
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1188,31 +1194,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1221,119 +1224,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1348,14 +1354,15 @@
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1863,7 +1870,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1877,7 +1884,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1891,7 +1898,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1905,7 +1912,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1919,7 +1926,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1933,7 +1940,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1947,7 +1954,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1961,7 +1968,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1975,7 +1982,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1989,7 +1996,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2003,7 +2010,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2017,7 +2024,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2031,7 +2038,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2045,7 +2052,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2059,7 +2066,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2073,7 +2080,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2087,7 +2094,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2101,7 +2108,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2115,7 +2122,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2129,7 +2136,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2143,7 +2150,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2157,7 +2164,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2171,7 +2178,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2185,7 +2192,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2241,7 +2248,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{F5F2C095-8E0A-F1B7-9076-2F694ACB84B1}">
+    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{F0D17417-56BE-54F4-B9CF-4069C52FD021}">
       <tableStyleElement type="wholeTable" dxfId="61"/>
       <tableStyleElement type="headerRow" dxfId="60"/>
       <tableStyleElement type="firstRowStripe" dxfId="59"/>
@@ -3261,8 +3268,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:BF50">
-  <sortState ref="A2:BF50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:BF51">
+  <sortState ref="A1:BF51">
     <sortCondition ref="D2:D50"/>
   </sortState>
   <tableColumns count="58">
@@ -3533,7 +3540,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BF50"/>
+  <dimension ref="A1:BF51"/>
   <sheetFormatPr defaultColWidth="12.6285714285714" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="7" width="18.8761904761905" customWidth="1"/>
@@ -3828,110 +3835,110 @@
       <c r="AE2" s="4">
         <v>0.001</v>
       </c>
-      <c r="AF2" s="7">
+      <c r="AF2" s="6">
         <v>11</v>
       </c>
-      <c r="AG2" s="8">
+      <c r="AG2" s="7">
         <f>IF(H2=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH2" s="8">
+      <c r="AH2" s="7">
         <f>IF(I2=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI2" s="8">
+      <c r="AI2" s="7">
         <f>IF(J2=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ2" s="8">
+      <c r="AJ2" s="7">
         <f>IF(K2=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK2" s="8">
+      <c r="AK2" s="7">
         <f>IF(L2=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL2" s="8">
+      <c r="AL2" s="7">
         <f>IF(M2=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM2" s="8">
+      <c r="AM2" s="7">
         <f>IF(N2=N$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AN2" s="8">
+      <c r="AN2" s="7">
         <f>IF(O2=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO2" s="8">
+      <c r="AO2" s="7">
         <f>IF(P2=P$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP2" s="8">
+      <c r="AP2" s="7">
         <f>IF(Q2=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ2" s="8">
+      <c r="AQ2" s="7">
         <f>IF(R2=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR2" s="8">
+      <c r="AR2" s="7">
         <f>IF(S2=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS2" s="8">
+      <c r="AS2" s="7">
         <f>IF(T2=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT2" s="8">
+      <c r="AT2" s="7">
         <f>IF(U2=U$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU2" s="8">
+      <c r="AU2" s="7">
         <f>IF(V2=V$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV2" s="8">
+      <c r="AV2" s="7">
         <f>IF(W2=W$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AW2" s="8">
+      <c r="AW2" s="7">
         <f>IF(X2=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX2" s="8">
+      <c r="AX2" s="7">
         <f>IF(Y2=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY2" s="8">
+      <c r="AY2" s="7">
         <f>IF(Z2=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ2" s="8">
+      <c r="AZ2" s="7">
         <f>IF(AA2=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA2" s="8">
+      <c r="BA2" s="7">
         <f>IF(AB2=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB2" s="8">
+      <c r="BB2" s="7">
         <f>IF(AC2=AC$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC2" s="8">
+      <c r="BC2" s="7">
         <f>IF(AD2=AD$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD2" s="8">
+      <c r="BD2" s="7">
         <f>IF(AE2=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE2" s="8">
+      <c r="BE2" s="7">
         <f>IF(AF2=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF2" s="8">
+      <c r="BF2" s="7">
         <f>SUM(AG2:BE2)*4</f>
         <v>28</v>
       </c>
@@ -4033,107 +4040,107 @@
       <c r="AF3" s="4">
         <v>11</v>
       </c>
-      <c r="AG3" s="8">
+      <c r="AG3" s="7">
         <f>IF(H3=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH3" s="8">
+      <c r="AH3" s="7">
         <f>IF(I3=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI3" s="8">
+      <c r="AI3" s="7">
         <f>IF(J3=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ3" s="8">
+      <c r="AJ3" s="7">
         <f>IF(K3=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK3" s="8">
+      <c r="AK3" s="7">
         <f>IF(L3=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL3" s="8">
+      <c r="AL3" s="7">
         <f>IF(M3=M$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM3" s="8">
+      <c r="AM3" s="7">
         <f>IF(N3=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN3" s="8">
+      <c r="AN3" s="7">
         <f>IF(O3=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO3" s="8">
+      <c r="AO3" s="7">
         <f>IF(P3=P$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP3" s="8">
+      <c r="AP3" s="7">
         <f>IF(Q3=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ3" s="8">
+      <c r="AQ3" s="7">
         <f>IF(R3=R$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR3" s="8">
+      <c r="AR3" s="7">
         <f>IF(S3=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS3" s="8">
+      <c r="AS3" s="7">
         <f>IF(T3=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT3" s="8">
+      <c r="AT3" s="7">
         <f>IF(U3=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU3" s="8">
+      <c r="AU3" s="7">
         <f>IF(V3=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV3" s="8">
+      <c r="AV3" s="7">
         <f>IF(W3=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW3" s="8">
+      <c r="AW3" s="7">
         <f>IF(X3=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX3" s="8">
+      <c r="AX3" s="7">
         <f>IF(Y3=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY3" s="8">
+      <c r="AY3" s="7">
         <f>IF(Z3=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ3" s="8">
+      <c r="AZ3" s="7">
         <f>IF(AA3=AA$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BA3" s="8">
+      <c r="BA3" s="7">
         <f>IF(AB3=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB3" s="8">
+      <c r="BB3" s="7">
         <f>IF(AC3=AC$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC3" s="8">
+      <c r="BC3" s="7">
         <f>IF(AD3=AD$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD3" s="8">
+      <c r="BD3" s="7">
         <f>IF(AE3=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE3" s="8">
+      <c r="BE3" s="7">
         <f>IF(AF3=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF3" s="8">
+      <c r="BF3" s="7">
         <f>SUM(AG3:BE3)*4</f>
         <v>36</v>
       </c>
@@ -4235,107 +4242,107 @@
       <c r="AF4" s="4">
         <v>2</v>
       </c>
-      <c r="AG4" s="8">
+      <c r="AG4" s="7">
         <f>IF(H4=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH4" s="8">
+      <c r="AH4" s="7">
         <f>IF(I4=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI4" s="8">
+      <c r="AI4" s="7">
         <f>IF(J4=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ4" s="8">
+      <c r="AJ4" s="7">
         <f>IF(K4=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK4" s="8">
+      <c r="AK4" s="7">
         <f>IF(L4=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL4" s="8">
+      <c r="AL4" s="7">
         <f>IF(M4=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM4" s="8">
+      <c r="AM4" s="7">
         <f>IF(N4=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN4" s="8">
+      <c r="AN4" s="7">
         <f>IF(O4=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO4" s="8">
+      <c r="AO4" s="7">
         <f>IF(P4=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP4" s="8">
+      <c r="AP4" s="7">
         <f>IF(Q4=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ4" s="8">
+      <c r="AQ4" s="7">
         <f>IF(R4=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR4" s="8">
+      <c r="AR4" s="7">
         <f>IF(S4=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS4" s="8">
+      <c r="AS4" s="7">
         <f>IF(T4=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT4" s="8">
+      <c r="AT4" s="7">
         <f>IF(U4=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU4" s="8">
+      <c r="AU4" s="7">
         <f>IF(V4=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV4" s="8">
+      <c r="AV4" s="7">
         <f>IF(W4=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW4" s="8">
+      <c r="AW4" s="7">
         <f>IF(X4=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX4" s="8">
+      <c r="AX4" s="7">
         <f>IF(Y4=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY4" s="8">
+      <c r="AY4" s="7">
         <f>IF(Z4=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ4" s="8">
+      <c r="AZ4" s="7">
         <f>IF(AA4=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA4" s="8">
+      <c r="BA4" s="7">
         <f>IF(AB4=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB4" s="8">
+      <c r="BB4" s="7">
         <f>IF(AC4=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC4" s="8">
+      <c r="BC4" s="7">
         <f>IF(AD4=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD4" s="8">
+      <c r="BD4" s="7">
         <f>IF(AE4=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE4" s="8">
+      <c r="BE4" s="7">
         <f>IF(AF4=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF4" s="8">
+      <c r="BF4" s="7">
         <f>SUM(AG4:BE4)*4</f>
         <v>84</v>
       </c>
@@ -4437,107 +4444,107 @@
       <c r="AF5" s="4">
         <v>2</v>
       </c>
-      <c r="AG5" s="8">
+      <c r="AG5" s="7">
         <f>IF(H5=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH5" s="8">
+      <c r="AH5" s="7">
         <f>IF(I5=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI5" s="8">
+      <c r="AI5" s="7">
         <f>IF(J5=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ5" s="8">
+      <c r="AJ5" s="7">
         <f>IF(K5=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK5" s="8">
+      <c r="AK5" s="7">
         <f>IF(L5=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL5" s="8">
+      <c r="AL5" s="7">
         <f>IF(M5=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM5" s="8">
+      <c r="AM5" s="7">
         <f>IF(N5=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN5" s="8">
+      <c r="AN5" s="7">
         <f>IF(O5=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO5" s="8">
+      <c r="AO5" s="7">
         <f>IF(P5=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP5" s="8">
+      <c r="AP5" s="7">
         <f>IF(Q5=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ5" s="8">
+      <c r="AQ5" s="7">
         <f>IF(R5=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR5" s="8">
+      <c r="AR5" s="7">
         <f>IF(S5=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS5" s="8">
+      <c r="AS5" s="7">
         <f>IF(T5=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT5" s="8">
+      <c r="AT5" s="7">
         <f>IF(U5=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU5" s="8">
+      <c r="AU5" s="7">
         <f>IF(V5=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV5" s="8">
+      <c r="AV5" s="7">
         <f>IF(W5=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW5" s="8">
+      <c r="AW5" s="7">
         <f>IF(X5=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX5" s="8">
+      <c r="AX5" s="7">
         <f>IF(Y5=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY5" s="8">
+      <c r="AY5" s="7">
         <f>IF(Z5=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ5" s="8">
+      <c r="AZ5" s="7">
         <f>IF(AA5=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA5" s="8">
+      <c r="BA5" s="7">
         <f>IF(AB5=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB5" s="8">
+      <c r="BB5" s="7">
         <f>IF(AC5=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC5" s="8">
+      <c r="BC5" s="7">
         <f>IF(AD5=AD$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD5" s="8">
+      <c r="BD5" s="7">
         <f>IF(AE5=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE5" s="8">
+      <c r="BE5" s="7">
         <f>IF(AF5=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF5" s="8">
+      <c r="BF5" s="7">
         <f>SUM(AG5:BE5)*4</f>
         <v>88</v>
       </c>
@@ -4639,107 +4646,107 @@
       <c r="AF6" s="4">
         <v>3</v>
       </c>
-      <c r="AG6" s="8">
+      <c r="AG6" s="7">
         <f>IF(H6=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH6" s="8">
+      <c r="AH6" s="7">
         <f>IF(I6=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI6" s="8">
+      <c r="AI6" s="7">
         <f>IF(J6=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ6" s="8">
+      <c r="AJ6" s="7">
         <f>IF(K6=K$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AK6" s="8">
+      <c r="AK6" s="7">
         <f>IF(L6=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL6" s="8">
+      <c r="AL6" s="7">
         <f>IF(M6=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM6" s="8">
+      <c r="AM6" s="7">
         <f>IF(N6=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN6" s="8">
+      <c r="AN6" s="7">
         <f>IF(O6=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO6" s="8">
+      <c r="AO6" s="7">
         <f>IF(P6=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP6" s="8">
+      <c r="AP6" s="7">
         <f>IF(Q6=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ6" s="8">
+      <c r="AQ6" s="7">
         <f>IF(R6=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR6" s="8">
+      <c r="AR6" s="7">
         <f>IF(S6=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS6" s="8">
+      <c r="AS6" s="7">
         <f>IF(T6=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT6" s="8">
+      <c r="AT6" s="7">
         <f>IF(U6=U$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU6" s="8">
+      <c r="AU6" s="7">
         <f>IF(V6=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV6" s="8">
+      <c r="AV6" s="7">
         <f>IF(W6=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW6" s="8">
+      <c r="AW6" s="7">
         <f>IF(X6=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX6" s="8">
+      <c r="AX6" s="7">
         <f>IF(Y6=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY6" s="8">
+      <c r="AY6" s="7">
         <f>IF(Z6=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ6" s="8">
+      <c r="AZ6" s="7">
         <f>IF(AA6=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA6" s="8">
+      <c r="BA6" s="7">
         <f>IF(AB6=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB6" s="8">
+      <c r="BB6" s="7">
         <f>IF(AC6=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC6" s="8">
+      <c r="BC6" s="7">
         <f>IF(AD6=AD$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD6" s="8">
+      <c r="BD6" s="7">
         <f>IF(AE6=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE6" s="8">
+      <c r="BE6" s="7">
         <f>IF(AF6=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF6" s="8">
+      <c r="BF6" s="7">
         <f>SUM(AG6:BE6)*4</f>
         <v>80</v>
       </c>
@@ -4841,107 +4848,107 @@
       <c r="AF7" s="4">
         <v>4</v>
       </c>
-      <c r="AG7" s="8">
+      <c r="AG7" s="7">
         <f>IF(H7=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH7" s="8">
+      <c r="AH7" s="7">
         <f>IF(I7=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI7" s="8">
+      <c r="AI7" s="7">
         <f>IF(J7=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ7" s="8">
+      <c r="AJ7" s="7">
         <f>IF(K7=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK7" s="8">
+      <c r="AK7" s="7">
         <f>IF(L7=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL7" s="8">
+      <c r="AL7" s="7">
         <f>IF(M7=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM7" s="8">
+      <c r="AM7" s="7">
         <f>IF(N7=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN7" s="8">
+      <c r="AN7" s="7">
         <f>IF(O7=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO7" s="8">
+      <c r="AO7" s="7">
         <f>IF(P7=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP7" s="8">
+      <c r="AP7" s="7">
         <f>IF(Q7=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ7" s="8">
+      <c r="AQ7" s="7">
         <f>IF(R7=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR7" s="8">
+      <c r="AR7" s="7">
         <f>IF(S7=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS7" s="8">
+      <c r="AS7" s="7">
         <f>IF(T7=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT7" s="8">
+      <c r="AT7" s="7">
         <f>IF(U7=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU7" s="8">
+      <c r="AU7" s="7">
         <f>IF(V7=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV7" s="8">
+      <c r="AV7" s="7">
         <f>IF(W7=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW7" s="8">
+      <c r="AW7" s="7">
         <f>IF(X7=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX7" s="8">
+      <c r="AX7" s="7">
         <f>IF(Y7=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY7" s="8">
+      <c r="AY7" s="7">
         <f>IF(Z7=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ7" s="8">
+      <c r="AZ7" s="7">
         <f>IF(AA7=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA7" s="8">
+      <c r="BA7" s="7">
         <f>IF(AB7=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB7" s="8">
+      <c r="BB7" s="7">
         <f>IF(AC7=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC7" s="8">
+      <c r="BC7" s="7">
         <f>IF(AD7=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD7" s="8">
+      <c r="BD7" s="7">
         <f>IF(AE7=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE7" s="8">
+      <c r="BE7" s="7">
         <f>IF(AF7=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF7" s="8">
+      <c r="BF7" s="7">
         <f>SUM(AG7:BE7)*4</f>
         <v>88</v>
       </c>
@@ -5043,107 +5050,107 @@
       <c r="AF8" s="4">
         <v>3</v>
       </c>
-      <c r="AG8" s="8">
+      <c r="AG8" s="7">
         <f>IF(H8=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH8" s="8">
+      <c r="AH8" s="7">
         <f>IF(I8=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI8" s="8">
+      <c r="AI8" s="7">
         <f>IF(J8=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ8" s="8">
+      <c r="AJ8" s="7">
         <f>IF(K8=K$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AK8" s="8">
+      <c r="AK8" s="7">
         <f>IF(L8=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL8" s="8">
+      <c r="AL8" s="7">
         <f>IF(M8=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM8" s="8">
+      <c r="AM8" s="7">
         <f>IF(N8=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN8" s="8">
+      <c r="AN8" s="7">
         <f>IF(O8=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO8" s="8">
+      <c r="AO8" s="7">
         <f>IF(P8=P$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP8" s="8">
+      <c r="AP8" s="7">
         <f>IF(Q8=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ8" s="8">
+      <c r="AQ8" s="7">
         <f>IF(R8=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR8" s="8">
+      <c r="AR8" s="7">
         <f>IF(S8=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS8" s="8">
+      <c r="AS8" s="7">
         <f>IF(T8=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT8" s="8">
+      <c r="AT8" s="7">
         <f>IF(U8=U$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU8" s="8">
+      <c r="AU8" s="7">
         <f>IF(V8=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV8" s="8">
+      <c r="AV8" s="7">
         <f>IF(W8=W$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AW8" s="8">
+      <c r="AW8" s="7">
         <f>IF(X8=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX8" s="8">
+      <c r="AX8" s="7">
         <f>IF(Y8=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY8" s="8">
+      <c r="AY8" s="7">
         <f>IF(Z8=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ8" s="8">
+      <c r="AZ8" s="7">
         <f>IF(AA8=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA8" s="8">
+      <c r="BA8" s="7">
         <f>IF(AB8=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB8" s="8">
+      <c r="BB8" s="7">
         <f>IF(AC8=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC8" s="8">
+      <c r="BC8" s="7">
         <f>IF(AD8=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD8" s="8">
+      <c r="BD8" s="7">
         <f>IF(AE8=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE8" s="8">
+      <c r="BE8" s="7">
         <f>IF(AF8=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF8" s="8">
+      <c r="BF8" s="7">
         <f>SUM(AG8:BE8)*4</f>
         <v>68</v>
       </c>
@@ -5245,107 +5252,107 @@
       <c r="AF9" s="4">
         <v>17</v>
       </c>
-      <c r="AG9" s="8">
+      <c r="AG9" s="7">
         <f>IF(H9=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH9" s="8">
+      <c r="AH9" s="7">
         <f>IF(I9=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI9" s="8">
+      <c r="AI9" s="7">
         <f>IF(J9=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ9" s="8">
+      <c r="AJ9" s="7">
         <f>IF(K9=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK9" s="8">
+      <c r="AK9" s="7">
         <f>IF(L9=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL9" s="8">
+      <c r="AL9" s="7">
         <f>IF(M9=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM9" s="8">
+      <c r="AM9" s="7">
         <f>IF(N9=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN9" s="8">
+      <c r="AN9" s="7">
         <f>IF(O9=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO9" s="8">
+      <c r="AO9" s="7">
         <f>IF(P9=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP9" s="8">
+      <c r="AP9" s="7">
         <f>IF(Q9=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ9" s="8">
+      <c r="AQ9" s="7">
         <f>IF(R9=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR9" s="8">
+      <c r="AR9" s="7">
         <f>IF(S9=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS9" s="8">
+      <c r="AS9" s="7">
         <f>IF(T9=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT9" s="8">
+      <c r="AT9" s="7">
         <f>IF(U9=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU9" s="8">
+      <c r="AU9" s="7">
         <f>IF(V9=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV9" s="8">
+      <c r="AV9" s="7">
         <f>IF(W9=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW9" s="8">
+      <c r="AW9" s="7">
         <f>IF(X9=X$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AX9" s="8">
+      <c r="AX9" s="7">
         <f>IF(Y9=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY9" s="8">
+      <c r="AY9" s="7">
         <f>IF(Z9=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ9" s="8">
+      <c r="AZ9" s="7">
         <f>IF(AA9=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA9" s="8">
+      <c r="BA9" s="7">
         <f>IF(AB9=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB9" s="8">
+      <c r="BB9" s="7">
         <f>IF(AC9=AC$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC9" s="8">
+      <c r="BC9" s="7">
         <f>IF(AD9=AD$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD9" s="8">
+      <c r="BD9" s="7">
         <f>IF(AE9=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE9" s="8">
+      <c r="BE9" s="7">
         <f>IF(AF9=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF9" s="8">
+      <c r="BF9" s="7">
         <f>SUM(AG9:BE9)*4</f>
         <v>64</v>
       </c>
@@ -5447,107 +5454,107 @@
       <c r="AF10" s="4">
         <v>3</v>
       </c>
-      <c r="AG10" s="8">
+      <c r="AG10" s="7">
         <f>IF(H10=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH10" s="8">
+      <c r="AH10" s="7">
         <f>IF(I10=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="8">
+      <c r="AI10" s="7">
         <f>IF(J10=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="8">
+      <c r="AJ10" s="7">
         <f>IF(K10=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK10" s="8">
+      <c r="AK10" s="7">
         <f>IF(L10=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL10" s="8">
+      <c r="AL10" s="7">
         <f>IF(M10=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM10" s="8">
+      <c r="AM10" s="7">
         <f>IF(N10=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN10" s="8">
+      <c r="AN10" s="7">
         <f>IF(O10=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="8">
+      <c r="AO10" s="7">
         <f>IF(P10=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP10" s="8">
+      <c r="AP10" s="7">
         <f>IF(Q10=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="8">
+      <c r="AQ10" s="7">
         <f>IF(R10=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR10" s="8">
+      <c r="AR10" s="7">
         <f>IF(S10=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS10" s="8">
+      <c r="AS10" s="7">
         <f>IF(T10=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT10" s="8">
+      <c r="AT10" s="7">
         <f>IF(U10=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU10" s="8">
+      <c r="AU10" s="7">
         <f>IF(V10=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV10" s="8">
+      <c r="AV10" s="7">
         <f>IF(W10=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW10" s="8">
+      <c r="AW10" s="7">
         <f>IF(X10=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX10" s="8">
+      <c r="AX10" s="7">
         <f>IF(Y10=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY10" s="8">
+      <c r="AY10" s="7">
         <f>IF(Z10=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ10" s="8">
+      <c r="AZ10" s="7">
         <f>IF(AA10=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA10" s="8">
+      <c r="BA10" s="7">
         <f>IF(AB10=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB10" s="8">
+      <c r="BB10" s="7">
         <f>IF(AC10=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC10" s="8">
+      <c r="BC10" s="7">
         <f>IF(AD10=AD$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD10" s="8">
+      <c r="BD10" s="7">
         <f>IF(AE10=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE10" s="8">
+      <c r="BE10" s="7">
         <f>IF(AF10=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF10" s="8">
+      <c r="BF10" s="7">
         <f>SUM(AG10:BE10)*4</f>
         <v>72</v>
       </c>
@@ -5649,107 +5656,107 @@
       <c r="AF11" s="4">
         <v>3</v>
       </c>
-      <c r="AG11" s="8">
+      <c r="AG11" s="7">
         <f>IF(H11=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH11" s="8">
+      <c r="AH11" s="7">
         <f>IF(I11=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI11" s="8">
+      <c r="AI11" s="7">
         <f>IF(J11=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ11" s="8">
+      <c r="AJ11" s="7">
         <f>IF(K11=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK11" s="8">
+      <c r="AK11" s="7">
         <f>IF(L11=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL11" s="8">
+      <c r="AL11" s="7">
         <f>IF(M11=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM11" s="8">
+      <c r="AM11" s="7">
         <f>IF(N11=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN11" s="8">
+      <c r="AN11" s="7">
         <f>IF(O11=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO11" s="8">
+      <c r="AO11" s="7">
         <f>IF(P11=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP11" s="8">
+      <c r="AP11" s="7">
         <f>IF(Q11=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ11" s="8">
+      <c r="AQ11" s="7">
         <f>IF(R11=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR11" s="8">
+      <c r="AR11" s="7">
         <f>IF(S11=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS11" s="8">
+      <c r="AS11" s="7">
         <f>IF(T11=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT11" s="8">
+      <c r="AT11" s="7">
         <f>IF(U11=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU11" s="8">
+      <c r="AU11" s="7">
         <f>IF(V11=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV11" s="8">
+      <c r="AV11" s="7">
         <f>IF(W11=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW11" s="8">
+      <c r="AW11" s="7">
         <f>IF(X11=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX11" s="8">
+      <c r="AX11" s="7">
         <f>IF(Y11=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY11" s="8">
+      <c r="AY11" s="7">
         <f>IF(Z11=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ11" s="8">
+      <c r="AZ11" s="7">
         <f>IF(AA11=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA11" s="8">
+      <c r="BA11" s="7">
         <f>IF(AB11=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB11" s="8">
+      <c r="BB11" s="7">
         <f>IF(AC11=AC$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC11" s="8">
+      <c r="BC11" s="7">
         <f>IF(AD11=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD11" s="8">
+      <c r="BD11" s="7">
         <f>IF(AE11=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE11" s="8">
+      <c r="BE11" s="7">
         <f>IF(AF11=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF11" s="8">
+      <c r="BF11" s="7">
         <f>SUM(AG11:BE11)*4</f>
         <v>88</v>
       </c>
@@ -5851,107 +5858,107 @@
       <c r="AF12" s="4">
         <v>3</v>
       </c>
-      <c r="AG12" s="8">
+      <c r="AG12" s="7">
         <f>IF(H12=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH12" s="8">
+      <c r="AH12" s="7">
         <f>IF(I12=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI12" s="8">
+      <c r="AI12" s="7">
         <f>IF(J12=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ12" s="8">
+      <c r="AJ12" s="7">
         <f>IF(K12=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK12" s="8">
+      <c r="AK12" s="7">
         <f>IF(L12=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL12" s="8">
+      <c r="AL12" s="7">
         <f>IF(M12=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM12" s="8">
+      <c r="AM12" s="7">
         <f>IF(N12=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN12" s="8">
+      <c r="AN12" s="7">
         <f>IF(O12=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO12" s="8">
+      <c r="AO12" s="7">
         <f>IF(P12=P$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP12" s="8">
+      <c r="AP12" s="7">
         <f>IF(Q12=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ12" s="8">
+      <c r="AQ12" s="7">
         <f>IF(R12=R$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR12" s="8">
+      <c r="AR12" s="7">
         <f>IF(S12=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS12" s="8">
+      <c r="AS12" s="7">
         <f>IF(T12=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT12" s="8">
+      <c r="AT12" s="7">
         <f>IF(U12=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU12" s="8">
+      <c r="AU12" s="7">
         <f>IF(V12=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV12" s="8">
+      <c r="AV12" s="7">
         <f>IF(W12=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW12" s="8">
+      <c r="AW12" s="7">
         <f>IF(X12=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX12" s="8">
+      <c r="AX12" s="7">
         <f>IF(Y12=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY12" s="8">
+      <c r="AY12" s="7">
         <f>IF(Z12=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ12" s="8">
+      <c r="AZ12" s="7">
         <f>IF(AA12=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA12" s="8">
+      <c r="BA12" s="7">
         <f>IF(AB12=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB12" s="8">
+      <c r="BB12" s="7">
         <f>IF(AC12=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC12" s="8">
+      <c r="BC12" s="7">
         <f>IF(AD12=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD12" s="8">
+      <c r="BD12" s="7">
         <f>IF(AE12=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE12" s="8">
+      <c r="BE12" s="7">
         <f>IF(AF12=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF12" s="8">
+      <c r="BF12" s="7">
         <f>SUM(AG12:BE12)*4</f>
         <v>68</v>
       </c>
@@ -6053,107 +6060,107 @@
       <c r="AF13" s="4">
         <v>2</v>
       </c>
-      <c r="AG13" s="8">
+      <c r="AG13" s="7">
         <f>IF(H13=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH13" s="8">
+      <c r="AH13" s="7">
         <f>IF(I13=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI13" s="8">
+      <c r="AI13" s="7">
         <f>IF(J13=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ13" s="8">
+      <c r="AJ13" s="7">
         <f>IF(K13=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK13" s="8">
+      <c r="AK13" s="7">
         <f>IF(L13=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL13" s="8">
+      <c r="AL13" s="7">
         <f>IF(M13=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM13" s="8">
+      <c r="AM13" s="7">
         <f>IF(N13=N$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AN13" s="8">
+      <c r="AN13" s="7">
         <f>IF(O13=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO13" s="8">
+      <c r="AO13" s="7">
         <f>IF(P13=P$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP13" s="8">
+      <c r="AP13" s="7">
         <f>IF(Q13=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="8">
+      <c r="AQ13" s="7">
         <f>IF(R13=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR13" s="8">
+      <c r="AR13" s="7">
         <f>IF(S13=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS13" s="8">
+      <c r="AS13" s="7">
         <f>IF(T13=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT13" s="8">
+      <c r="AT13" s="7">
         <f>IF(U13=U$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU13" s="8">
+      <c r="AU13" s="7">
         <f>IF(V13=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV13" s="8">
+      <c r="AV13" s="7">
         <f>IF(W13=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW13" s="8">
+      <c r="AW13" s="7">
         <f>IF(X13=X$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AX13" s="8">
+      <c r="AX13" s="7">
         <f>IF(Y13=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY13" s="8">
+      <c r="AY13" s="7">
         <f>IF(Z13=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ13" s="8">
+      <c r="AZ13" s="7">
         <f>IF(AA13=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA13" s="8">
+      <c r="BA13" s="7">
         <f>IF(AB13=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB13" s="8">
+      <c r="BB13" s="7">
         <f>IF(AC13=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC13" s="8">
+      <c r="BC13" s="7">
         <f>IF(AD13=AD$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD13" s="8">
+      <c r="BD13" s="7">
         <f>IF(AE13=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE13" s="8">
+      <c r="BE13" s="7">
         <f>IF(AF13=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF13" s="8">
+      <c r="BF13" s="7">
         <f>SUM(AG13:BE13)*4</f>
         <v>44</v>
       </c>
@@ -6255,107 +6262,107 @@
       <c r="AF14" s="4">
         <v>3</v>
       </c>
-      <c r="AG14" s="8">
+      <c r="AG14" s="7">
         <f>IF(H14=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH14" s="8">
+      <c r="AH14" s="7">
         <f>IF(I14=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI14" s="8">
+      <c r="AI14" s="7">
         <f>IF(J14=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ14" s="8">
+      <c r="AJ14" s="7">
         <f>IF(K14=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK14" s="8">
+      <c r="AK14" s="7">
         <f>IF(L14=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL14" s="8">
+      <c r="AL14" s="7">
         <f>IF(M14=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM14" s="8">
+      <c r="AM14" s="7">
         <f>IF(N14=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN14" s="8">
+      <c r="AN14" s="7">
         <f>IF(O14=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO14" s="8">
+      <c r="AO14" s="7">
         <f>IF(P14=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP14" s="8">
+      <c r="AP14" s="7">
         <f>IF(Q14=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ14" s="8">
+      <c r="AQ14" s="7">
         <f>IF(R14=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR14" s="8">
+      <c r="AR14" s="7">
         <f>IF(S14=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS14" s="8">
+      <c r="AS14" s="7">
         <f>IF(T14=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT14" s="8">
+      <c r="AT14" s="7">
         <f>IF(U14=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU14" s="8">
+      <c r="AU14" s="7">
         <f>IF(V14=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV14" s="8">
+      <c r="AV14" s="7">
         <f>IF(W14=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW14" s="8">
+      <c r="AW14" s="7">
         <f>IF(X14=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX14" s="8">
+      <c r="AX14" s="7">
         <f>IF(Y14=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY14" s="8">
+      <c r="AY14" s="7">
         <f>IF(Z14=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ14" s="8">
+      <c r="AZ14" s="7">
         <f>IF(AA14=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA14" s="8">
+      <c r="BA14" s="7">
         <f>IF(AB14=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB14" s="8">
+      <c r="BB14" s="7">
         <f>IF(AC14=AC$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC14" s="8">
+      <c r="BC14" s="7">
         <f>IF(AD14=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD14" s="8">
+      <c r="BD14" s="7">
         <f>IF(AE14=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE14" s="8">
+      <c r="BE14" s="7">
         <f>IF(AF14=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF14" s="8">
+      <c r="BF14" s="7">
         <f>SUM(AG14:BE14)*4</f>
         <v>84</v>
       </c>
@@ -6457,107 +6464,107 @@
       <c r="AF15" s="4">
         <v>3</v>
       </c>
-      <c r="AG15" s="8">
+      <c r="AG15" s="7">
         <f>IF(H15=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH15" s="8">
+      <c r="AH15" s="7">
         <f>IF(I15=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI15" s="8">
+      <c r="AI15" s="7">
         <f>IF(J15=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ15" s="8">
+      <c r="AJ15" s="7">
         <f>IF(K15=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK15" s="8">
+      <c r="AK15" s="7">
         <f>IF(L15=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL15" s="8">
+      <c r="AL15" s="7">
         <f>IF(M15=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM15" s="8">
+      <c r="AM15" s="7">
         <f>IF(N15=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN15" s="8">
+      <c r="AN15" s="7">
         <f>IF(O15=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="8">
+      <c r="AO15" s="7">
         <f>IF(P15=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP15" s="8">
+      <c r="AP15" s="7">
         <f>IF(Q15=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ15" s="8">
+      <c r="AQ15" s="7">
         <f>IF(R15=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR15" s="8">
+      <c r="AR15" s="7">
         <f>IF(S15=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS15" s="8">
+      <c r="AS15" s="7">
         <f>IF(T15=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT15" s="8">
+      <c r="AT15" s="7">
         <f>IF(U15=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU15" s="8">
+      <c r="AU15" s="7">
         <f>IF(V15=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV15" s="8">
+      <c r="AV15" s="7">
         <f>IF(W15=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW15" s="8">
+      <c r="AW15" s="7">
         <f>IF(X15=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX15" s="8">
+      <c r="AX15" s="7">
         <f>IF(Y15=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY15" s="8">
+      <c r="AY15" s="7">
         <f>IF(Z15=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ15" s="8">
+      <c r="AZ15" s="7">
         <f>IF(AA15=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA15" s="8">
+      <c r="BA15" s="7">
         <f>IF(AB15=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB15" s="8">
+      <c r="BB15" s="7">
         <f>IF(AC15=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC15" s="8">
+      <c r="BC15" s="7">
         <f>IF(AD15=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD15" s="8">
+      <c r="BD15" s="7">
         <f>IF(AE15=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE15" s="8">
+      <c r="BE15" s="7">
         <f>IF(AF15=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF15" s="8">
+      <c r="BF15" s="7">
         <f>SUM(AG15:BE15)*4</f>
         <v>92</v>
       </c>
@@ -6659,107 +6666,107 @@
       <c r="AF16" s="4">
         <v>3</v>
       </c>
-      <c r="AG16" s="8">
+      <c r="AG16" s="7">
         <f>IF(H16=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH16" s="8">
+      <c r="AH16" s="7">
         <f>IF(I16=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI16" s="8">
+      <c r="AI16" s="7">
         <f>IF(J16=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ16" s="8">
+      <c r="AJ16" s="7">
         <f>IF(K16=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK16" s="8">
+      <c r="AK16" s="7">
         <f>IF(L16=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL16" s="8">
+      <c r="AL16" s="7">
         <f>IF(M16=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM16" s="8">
+      <c r="AM16" s="7">
         <f>IF(N16=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN16" s="8">
+      <c r="AN16" s="7">
         <f>IF(O16=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO16" s="8">
+      <c r="AO16" s="7">
         <f>IF(P16=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP16" s="8">
+      <c r="AP16" s="7">
         <f>IF(Q16=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ16" s="8">
+      <c r="AQ16" s="7">
         <f>IF(R16=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR16" s="8">
+      <c r="AR16" s="7">
         <f>IF(S16=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS16" s="8">
+      <c r="AS16" s="7">
         <f>IF(T16=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT16" s="8">
+      <c r="AT16" s="7">
         <f>IF(U16=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU16" s="8">
+      <c r="AU16" s="7">
         <f>IF(V16=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV16" s="8">
+      <c r="AV16" s="7">
         <f>IF(W16=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW16" s="8">
+      <c r="AW16" s="7">
         <f>IF(X16=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX16" s="8">
+      <c r="AX16" s="7">
         <f>IF(Y16=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY16" s="8">
+      <c r="AY16" s="7">
         <f>IF(Z16=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ16" s="8">
+      <c r="AZ16" s="7">
         <f>IF(AA16=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA16" s="8">
+      <c r="BA16" s="7">
         <f>IF(AB16=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB16" s="8">
+      <c r="BB16" s="7">
         <f>IF(AC16=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC16" s="8">
+      <c r="BC16" s="7">
         <f>IF(AD16=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD16" s="8">
+      <c r="BD16" s="7">
         <f>IF(AE16=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE16" s="8">
+      <c r="BE16" s="7">
         <f>IF(AF16=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF16" s="8">
+      <c r="BF16" s="7">
         <f>SUM(AG16:BE16)*4</f>
         <v>96</v>
       </c>
@@ -6861,107 +6868,107 @@
       <c r="AF17" s="4">
         <v>3</v>
       </c>
-      <c r="AG17" s="8">
+      <c r="AG17" s="7">
         <f>IF(H17=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH17" s="8">
+      <c r="AH17" s="7">
         <f>IF(I17=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI17" s="8">
+      <c r="AI17" s="7">
         <f>IF(J17=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ17" s="8">
+      <c r="AJ17" s="7">
         <f>IF(K17=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK17" s="8">
+      <c r="AK17" s="7">
         <f>IF(L17=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL17" s="8">
+      <c r="AL17" s="7">
         <f>IF(M17=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM17" s="8">
+      <c r="AM17" s="7">
         <f>IF(N17=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN17" s="8">
+      <c r="AN17" s="7">
         <f>IF(O17=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO17" s="8">
+      <c r="AO17" s="7">
         <f>IF(P17=P$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP17" s="8">
+      <c r="AP17" s="7">
         <f>IF(Q17=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ17" s="8">
+      <c r="AQ17" s="7">
         <f>IF(R17=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR17" s="8">
+      <c r="AR17" s="7">
         <f>IF(S17=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS17" s="8">
+      <c r="AS17" s="7">
         <f>IF(T17=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT17" s="8">
+      <c r="AT17" s="7">
         <f>IF(U17=U$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU17" s="8">
+      <c r="AU17" s="7">
         <f>IF(V17=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV17" s="8">
+      <c r="AV17" s="7">
         <f>IF(W17=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW17" s="8">
+      <c r="AW17" s="7">
         <f>IF(X17=X$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AX17" s="8">
+      <c r="AX17" s="7">
         <f>IF(Y17=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY17" s="8">
+      <c r="AY17" s="7">
         <f>IF(Z17=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ17" s="8">
+      <c r="AZ17" s="7">
         <f>IF(AA17=AA$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BA17" s="8">
+      <c r="BA17" s="7">
         <f>IF(AB17=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB17" s="8">
+      <c r="BB17" s="7">
         <f>IF(AC17=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC17" s="8">
+      <c r="BC17" s="7">
         <f>IF(AD17=AD$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD17" s="8">
+      <c r="BD17" s="7">
         <f>IF(AE17=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE17" s="8">
+      <c r="BE17" s="7">
         <f>IF(AF17=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF17" s="8">
+      <c r="BF17" s="7">
         <f>SUM(AG17:BE17)*4</f>
         <v>52</v>
       </c>
@@ -7063,107 +7070,107 @@
       <c r="AF18" s="4">
         <v>18</v>
       </c>
-      <c r="AG18" s="8">
+      <c r="AG18" s="7">
         <f>IF(H18=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH18" s="8">
+      <c r="AH18" s="7">
         <f>IF(I18=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI18" s="8">
+      <c r="AI18" s="7">
         <f>IF(J18=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ18" s="8">
+      <c r="AJ18" s="7">
         <f>IF(K18=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK18" s="8">
+      <c r="AK18" s="7">
         <f>IF(L18=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL18" s="8">
+      <c r="AL18" s="7">
         <f>IF(M18=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM18" s="8">
+      <c r="AM18" s="7">
         <f>IF(N18=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN18" s="8">
+      <c r="AN18" s="7">
         <f>IF(O18=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO18" s="8">
+      <c r="AO18" s="7">
         <f>IF(P18=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP18" s="8">
+      <c r="AP18" s="7">
         <f>IF(Q18=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ18" s="8">
+      <c r="AQ18" s="7">
         <f>IF(R18=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR18" s="8">
+      <c r="AR18" s="7">
         <f>IF(S18=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS18" s="8">
+      <c r="AS18" s="7">
         <f>IF(T18=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT18" s="8">
+      <c r="AT18" s="7">
         <f>IF(U18=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU18" s="8">
+      <c r="AU18" s="7">
         <f>IF(V18=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV18" s="8">
+      <c r="AV18" s="7">
         <f>IF(W18=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW18" s="8">
+      <c r="AW18" s="7">
         <f>IF(X18=X$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AX18" s="8">
+      <c r="AX18" s="7">
         <f>IF(Y18=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY18" s="8">
+      <c r="AY18" s="7">
         <f>IF(Z18=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ18" s="8">
+      <c r="AZ18" s="7">
         <f>IF(AA18=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA18" s="8">
+      <c r="BA18" s="7">
         <f>IF(AB18=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB18" s="8">
+      <c r="BB18" s="7">
         <f>IF(AC18=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC18" s="8">
+      <c r="BC18" s="7">
         <f>IF(AD18=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD18" s="8">
+      <c r="BD18" s="7">
         <f>IF(AE18=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE18" s="8">
+      <c r="BE18" s="7">
         <f>IF(AF18=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF18" s="8">
+      <c r="BF18" s="7">
         <f>SUM(AG18:BE18)*4</f>
         <v>76</v>
       </c>
@@ -7265,107 +7272,107 @@
       <c r="AF19" s="4">
         <v>3</v>
       </c>
-      <c r="AG19" s="8">
+      <c r="AG19" s="7">
         <f>IF(H19=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH19" s="8">
+      <c r="AH19" s="7">
         <f>IF(I19=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI19" s="8">
+      <c r="AI19" s="7">
         <f>IF(J19=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ19" s="8">
+      <c r="AJ19" s="7">
         <f>IF(K19=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK19" s="8">
+      <c r="AK19" s="7">
         <f>IF(L19=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL19" s="8">
+      <c r="AL19" s="7">
         <f>IF(M19=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM19" s="8">
+      <c r="AM19" s="7">
         <f>IF(N19=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN19" s="8">
+      <c r="AN19" s="7">
         <f>IF(O19=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO19" s="8">
+      <c r="AO19" s="7">
         <f>IF(P19=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP19" s="8">
+      <c r="AP19" s="7">
         <f>IF(Q19=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ19" s="8">
+      <c r="AQ19" s="7">
         <f>IF(R19=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR19" s="8">
+      <c r="AR19" s="7">
         <f>IF(S19=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS19" s="8">
+      <c r="AS19" s="7">
         <f>IF(T19=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT19" s="8">
+      <c r="AT19" s="7">
         <f>IF(U19=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU19" s="8">
+      <c r="AU19" s="7">
         <f>IF(V19=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV19" s="8">
+      <c r="AV19" s="7">
         <f>IF(W19=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW19" s="8">
+      <c r="AW19" s="7">
         <f>IF(X19=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX19" s="8">
+      <c r="AX19" s="7">
         <f>IF(Y19=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY19" s="8">
+      <c r="AY19" s="7">
         <f>IF(Z19=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ19" s="8">
+      <c r="AZ19" s="7">
         <f>IF(AA19=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA19" s="8">
+      <c r="BA19" s="7">
         <f>IF(AB19=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB19" s="8">
+      <c r="BB19" s="7">
         <f>IF(AC19=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC19" s="8">
+      <c r="BC19" s="7">
         <f>IF(AD19=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD19" s="8">
+      <c r="BD19" s="7">
         <f>IF(AE19=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE19" s="8">
+      <c r="BE19" s="7">
         <f>IF(AF19=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF19" s="8">
+      <c r="BF19" s="7">
         <f>SUM(AG19:BE19)*4</f>
         <v>92</v>
       </c>
@@ -7467,107 +7474,107 @@
       <c r="AF20" s="4">
         <v>3</v>
       </c>
-      <c r="AG20" s="8">
+      <c r="AG20" s="7">
         <f>IF(H20=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH20" s="8">
+      <c r="AH20" s="7">
         <f>IF(I20=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI20" s="8">
+      <c r="AI20" s="7">
         <f>IF(J20=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ20" s="8">
+      <c r="AJ20" s="7">
         <f>IF(K20=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK20" s="8">
+      <c r="AK20" s="7">
         <f>IF(L20=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL20" s="8">
+      <c r="AL20" s="7">
         <f>IF(M20=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM20" s="8">
+      <c r="AM20" s="7">
         <f>IF(N20=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN20" s="8">
+      <c r="AN20" s="7">
         <f>IF(O20=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO20" s="8">
+      <c r="AO20" s="7">
         <f>IF(P20=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP20" s="8">
+      <c r="AP20" s="7">
         <f>IF(Q20=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ20" s="8">
+      <c r="AQ20" s="7">
         <f>IF(R20=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR20" s="8">
+      <c r="AR20" s="7">
         <f>IF(S20=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS20" s="8">
+      <c r="AS20" s="7">
         <f>IF(T20=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT20" s="8">
+      <c r="AT20" s="7">
         <f>IF(U20=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU20" s="8">
+      <c r="AU20" s="7">
         <f>IF(V20=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV20" s="8">
+      <c r="AV20" s="7">
         <f>IF(W20=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW20" s="8">
+      <c r="AW20" s="7">
         <f>IF(X20=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX20" s="8">
+      <c r="AX20" s="7">
         <f>IF(Y20=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY20" s="8">
+      <c r="AY20" s="7">
         <f>IF(Z20=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ20" s="8">
+      <c r="AZ20" s="7">
         <f>IF(AA20=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA20" s="8">
+      <c r="BA20" s="7">
         <f>IF(AB20=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB20" s="8">
+      <c r="BB20" s="7">
         <f>IF(AC20=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC20" s="8">
+      <c r="BC20" s="7">
         <f>IF(AD20=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD20" s="8">
+      <c r="BD20" s="7">
         <f>IF(AE20=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE20" s="8">
+      <c r="BE20" s="7">
         <f>IF(AF20=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF20" s="8">
+      <c r="BF20" s="7">
         <f>SUM(AG20:BE20)*4</f>
         <v>100</v>
       </c>
@@ -7669,107 +7676,107 @@
       <c r="AF21" s="4">
         <v>3</v>
       </c>
-      <c r="AG21" s="8">
+      <c r="AG21" s="7">
         <f>IF(H21=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH21" s="8">
+      <c r="AH21" s="7">
         <f>IF(I21=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI21" s="8">
+      <c r="AI21" s="7">
         <f>IF(J21=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ21" s="8">
+      <c r="AJ21" s="7">
         <f>IF(K21=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK21" s="8">
+      <c r="AK21" s="7">
         <f>IF(L21=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL21" s="8">
+      <c r="AL21" s="7">
         <f>IF(M21=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM21" s="8">
+      <c r="AM21" s="7">
         <f>IF(N21=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN21" s="8">
+      <c r="AN21" s="7">
         <f>IF(O21=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO21" s="8">
+      <c r="AO21" s="7">
         <f>IF(P21=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP21" s="8">
+      <c r="AP21" s="7">
         <f>IF(Q21=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ21" s="8">
+      <c r="AQ21" s="7">
         <f>IF(R21=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR21" s="8">
+      <c r="AR21" s="7">
         <f>IF(S21=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS21" s="8">
+      <c r="AS21" s="7">
         <f>IF(T21=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT21" s="8">
+      <c r="AT21" s="7">
         <f>IF(U21=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU21" s="8">
+      <c r="AU21" s="7">
         <f>IF(V21=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV21" s="8">
+      <c r="AV21" s="7">
         <f>IF(W21=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW21" s="8">
+      <c r="AW21" s="7">
         <f>IF(X21=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX21" s="8">
+      <c r="AX21" s="7">
         <f>IF(Y21=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY21" s="8">
+      <c r="AY21" s="7">
         <f>IF(Z21=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ21" s="8">
+      <c r="AZ21" s="7">
         <f>IF(AA21=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA21" s="8">
+      <c r="BA21" s="7">
         <f>IF(AB21=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB21" s="8">
+      <c r="BB21" s="7">
         <f>IF(AC21=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC21" s="8">
+      <c r="BC21" s="7">
         <f>IF(AD21=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD21" s="8">
+      <c r="BD21" s="7">
         <f>IF(AE21=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE21" s="8">
+      <c r="BE21" s="7">
         <f>IF(AF21=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF21" s="8">
+      <c r="BF21" s="7">
         <f>SUM(AG21:BE21)*4</f>
         <v>96</v>
       </c>
@@ -7871,107 +7878,107 @@
       <c r="AF22" s="4">
         <v>3</v>
       </c>
-      <c r="AG22" s="8">
+      <c r="AG22" s="7">
         <f>IF(H22=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH22" s="8">
+      <c r="AH22" s="7">
         <f>IF(I22=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI22" s="8">
+      <c r="AI22" s="7">
         <f>IF(J22=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ22" s="8">
+      <c r="AJ22" s="7">
         <f>IF(K22=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK22" s="8">
+      <c r="AK22" s="7">
         <f>IF(L22=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL22" s="8">
+      <c r="AL22" s="7">
         <f>IF(M22=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM22" s="8">
+      <c r="AM22" s="7">
         <f>IF(N22=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN22" s="8">
+      <c r="AN22" s="7">
         <f>IF(O22=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO22" s="8">
+      <c r="AO22" s="7">
         <f>IF(P22=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP22" s="8">
+      <c r="AP22" s="7">
         <f>IF(Q22=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ22" s="8">
+      <c r="AQ22" s="7">
         <f>IF(R22=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR22" s="8">
+      <c r="AR22" s="7">
         <f>IF(S22=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS22" s="8">
+      <c r="AS22" s="7">
         <f>IF(T22=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT22" s="8">
+      <c r="AT22" s="7">
         <f>IF(U22=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU22" s="8">
+      <c r="AU22" s="7">
         <f>IF(V22=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV22" s="8">
+      <c r="AV22" s="7">
         <f>IF(W22=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW22" s="8">
+      <c r="AW22" s="7">
         <f>IF(X22=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX22" s="8">
+      <c r="AX22" s="7">
         <f>IF(Y22=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY22" s="8">
+      <c r="AY22" s="7">
         <f>IF(Z22=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ22" s="8">
+      <c r="AZ22" s="7">
         <f>IF(AA22=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA22" s="8">
+      <c r="BA22" s="7">
         <f>IF(AB22=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB22" s="8">
+      <c r="BB22" s="7">
         <f>IF(AC22=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC22" s="8">
+      <c r="BC22" s="7">
         <f>IF(AD22=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD22" s="8">
+      <c r="BD22" s="7">
         <f>IF(AE22=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE22" s="8">
+      <c r="BE22" s="7">
         <f>IF(AF22=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF22" s="8">
+      <c r="BF22" s="7">
         <f>SUM(AG22:BE22)*4</f>
         <v>100</v>
       </c>
@@ -8073,107 +8080,107 @@
       <c r="AF23" s="4">
         <v>3</v>
       </c>
-      <c r="AG23" s="8">
+      <c r="AG23" s="7">
         <f>IF(H23=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH23" s="8">
+      <c r="AH23" s="7">
         <f>IF(I23=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI23" s="8">
+      <c r="AI23" s="7">
         <f>IF(J23=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ23" s="8">
+      <c r="AJ23" s="7">
         <f>IF(K23=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK23" s="8">
+      <c r="AK23" s="7">
         <f>IF(L23=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL23" s="8">
+      <c r="AL23" s="7">
         <f>IF(M23=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM23" s="8">
+      <c r="AM23" s="7">
         <f>IF(N23=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN23" s="8">
+      <c r="AN23" s="7">
         <f>IF(O23=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO23" s="8">
+      <c r="AO23" s="7">
         <f>IF(P23=P$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP23" s="8">
+      <c r="AP23" s="7">
         <f>IF(Q23=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ23" s="8">
+      <c r="AQ23" s="7">
         <f>IF(R23=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR23" s="8">
+      <c r="AR23" s="7">
         <f>IF(S23=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS23" s="8">
+      <c r="AS23" s="7">
         <f>IF(T23=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT23" s="8">
+      <c r="AT23" s="7">
         <f>IF(U23=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU23" s="8">
+      <c r="AU23" s="7">
         <f>IF(V23=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV23" s="8">
+      <c r="AV23" s="7">
         <f>IF(W23=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW23" s="8">
+      <c r="AW23" s="7">
         <f>IF(X23=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX23" s="8">
+      <c r="AX23" s="7">
         <f>IF(Y23=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY23" s="8">
+      <c r="AY23" s="7">
         <f>IF(Z23=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ23" s="8">
+      <c r="AZ23" s="7">
         <f>IF(AA23=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA23" s="8">
+      <c r="BA23" s="7">
         <f>IF(AB23=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB23" s="8">
+      <c r="BB23" s="7">
         <f>IF(AC23=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC23" s="8">
+      <c r="BC23" s="7">
         <f>IF(AD23=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD23" s="8">
+      <c r="BD23" s="7">
         <f>IF(AE23=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE23" s="8">
+      <c r="BE23" s="7">
         <f>IF(AF23=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF23" s="8">
+      <c r="BF23" s="7">
         <f>SUM(AG23:BE23)*4</f>
         <v>92</v>
       </c>
@@ -8275,107 +8282,107 @@
       <c r="AF24" s="4">
         <v>3</v>
       </c>
-      <c r="AG24" s="8">
+      <c r="AG24" s="7">
         <f>IF(H24=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH24" s="8">
+      <c r="AH24" s="7">
         <f>IF(I24=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI24" s="8">
+      <c r="AI24" s="7">
         <f>IF(J24=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ24" s="8">
+      <c r="AJ24" s="7">
         <f>IF(K24=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK24" s="8">
+      <c r="AK24" s="7">
         <f>IF(L24=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL24" s="8">
+      <c r="AL24" s="7">
         <f>IF(M24=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM24" s="8">
+      <c r="AM24" s="7">
         <f>IF(N24=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN24" s="8">
+      <c r="AN24" s="7">
         <f>IF(O24=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO24" s="8">
+      <c r="AO24" s="7">
         <f>IF(P24=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP24" s="8">
+      <c r="AP24" s="7">
         <f>IF(Q24=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ24" s="8">
+      <c r="AQ24" s="7">
         <f>IF(R24=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR24" s="8">
+      <c r="AR24" s="7">
         <f>IF(S24=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS24" s="8">
+      <c r="AS24" s="7">
         <f>IF(T24=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT24" s="8">
+      <c r="AT24" s="7">
         <f>IF(U24=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU24" s="8">
+      <c r="AU24" s="7">
         <f>IF(V24=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV24" s="8">
+      <c r="AV24" s="7">
         <f>IF(W24=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW24" s="8">
+      <c r="AW24" s="7">
         <f>IF(X24=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX24" s="8">
+      <c r="AX24" s="7">
         <f>IF(Y24=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY24" s="8">
+      <c r="AY24" s="7">
         <f>IF(Z24=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ24" s="8">
+      <c r="AZ24" s="7">
         <f>IF(AA24=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA24" s="8">
+      <c r="BA24" s="7">
         <f>IF(AB24=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB24" s="8">
+      <c r="BB24" s="7">
         <f>IF(AC24=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC24" s="8">
+      <c r="BC24" s="7">
         <f>IF(AD24=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD24" s="8">
+      <c r="BD24" s="7">
         <f>IF(AE24=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE24" s="8">
+      <c r="BE24" s="7">
         <f>IF(AF24=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF24" s="8">
+      <c r="BF24" s="7">
         <f>SUM(AG24:BE24)*4</f>
         <v>96</v>
       </c>
@@ -8477,107 +8484,107 @@
       <c r="AF25" s="4">
         <v>3</v>
       </c>
-      <c r="AG25" s="8">
+      <c r="AG25" s="7">
         <f>IF(H25=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH25" s="8">
+      <c r="AH25" s="7">
         <f>IF(I25=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI25" s="8">
+      <c r="AI25" s="7">
         <f>IF(J25=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ25" s="8">
+      <c r="AJ25" s="7">
         <f>IF(K25=K$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AK25" s="8">
+      <c r="AK25" s="7">
         <f>IF(L25=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL25" s="8">
+      <c r="AL25" s="7">
         <f>IF(M25=M$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM25" s="8">
+      <c r="AM25" s="7">
         <f>IF(N25=N$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AN25" s="8">
+      <c r="AN25" s="7">
         <f>IF(O25=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO25" s="8">
+      <c r="AO25" s="7">
         <f>IF(P25=P$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP25" s="8">
+      <c r="AP25" s="7">
         <f>IF(Q25=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ25" s="8">
+      <c r="AQ25" s="7">
         <f>IF(R25=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR25" s="8">
+      <c r="AR25" s="7">
         <f>IF(S25=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS25" s="8">
+      <c r="AS25" s="7">
         <f>IF(T25=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT25" s="8">
+      <c r="AT25" s="7">
         <f>IF(U25=U$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU25" s="8">
+      <c r="AU25" s="7">
         <f>IF(V25=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV25" s="8">
+      <c r="AV25" s="7">
         <f>IF(W25=W$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AW25" s="8">
+      <c r="AW25" s="7">
         <f>IF(X25=X$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AX25" s="8">
+      <c r="AX25" s="7">
         <f>IF(Y25=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY25" s="8">
+      <c r="AY25" s="7">
         <f>IF(Z25=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ25" s="8">
+      <c r="AZ25" s="7">
         <f>IF(AA25=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA25" s="8">
+      <c r="BA25" s="7">
         <f>IF(AB25=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB25" s="8">
+      <c r="BB25" s="7">
         <f>IF(AC25=AC$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC25" s="8">
+      <c r="BC25" s="7">
         <f>IF(AD25=AD$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BD25" s="8">
+      <c r="BD25" s="7">
         <f>IF(AE25=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE25" s="8">
+      <c r="BE25" s="7">
         <f>IF(AF25=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF25" s="8">
+      <c r="BF25" s="7">
         <f>SUM(AG25:BE25)*4</f>
         <v>32</v>
       </c>
@@ -8679,107 +8686,107 @@
       <c r="AF26" s="4">
         <v>3</v>
       </c>
-      <c r="AG26" s="8">
+      <c r="AG26" s="7">
         <f>IF(H26=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH26" s="8">
+      <c r="AH26" s="7">
         <f>IF(I26=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI26" s="8">
+      <c r="AI26" s="7">
         <f>IF(J26=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ26" s="8">
+      <c r="AJ26" s="7">
         <f>IF(K26=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK26" s="8">
+      <c r="AK26" s="7">
         <f>IF(L26=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL26" s="8">
+      <c r="AL26" s="7">
         <f>IF(M26=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM26" s="8">
+      <c r="AM26" s="7">
         <f>IF(N26=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN26" s="8">
+      <c r="AN26" s="7">
         <f>IF(O26=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO26" s="8">
+      <c r="AO26" s="7">
         <f>IF(P26=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP26" s="8">
+      <c r="AP26" s="7">
         <f>IF(Q26=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ26" s="8">
+      <c r="AQ26" s="7">
         <f>IF(R26=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR26" s="8">
+      <c r="AR26" s="7">
         <f>IF(S26=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS26" s="8">
+      <c r="AS26" s="7">
         <f>IF(T26=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT26" s="8">
+      <c r="AT26" s="7">
         <f>IF(U26=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU26" s="8">
+      <c r="AU26" s="7">
         <f>IF(V26=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV26" s="8">
+      <c r="AV26" s="7">
         <f>IF(W26=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW26" s="8">
+      <c r="AW26" s="7">
         <f>IF(X26=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX26" s="8">
+      <c r="AX26" s="7">
         <f>IF(Y26=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY26" s="8">
+      <c r="AY26" s="7">
         <f>IF(Z26=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ26" s="8">
+      <c r="AZ26" s="7">
         <f>IF(AA26=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA26" s="8">
+      <c r="BA26" s="7">
         <f>IF(AB26=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB26" s="8">
+      <c r="BB26" s="7">
         <f>IF(AC26=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC26" s="8">
+      <c r="BC26" s="7">
         <f>IF(AD26=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD26" s="8">
+      <c r="BD26" s="7">
         <f>IF(AE26=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE26" s="8">
+      <c r="BE26" s="7">
         <f>IF(AF26=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF26" s="8">
+      <c r="BF26" s="7">
         <f>SUM(AG26:BE26)*4</f>
         <v>96</v>
       </c>
@@ -8881,107 +8888,107 @@
       <c r="AF27" s="4">
         <v>3</v>
       </c>
-      <c r="AG27" s="8">
+      <c r="AG27" s="7">
         <f>IF(H27=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH27" s="8">
+      <c r="AH27" s="7">
         <f>IF(I27=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI27" s="8">
+      <c r="AI27" s="7">
         <f>IF(J27=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ27" s="8">
+      <c r="AJ27" s="7">
         <f>IF(K27=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK27" s="8">
+      <c r="AK27" s="7">
         <f>IF(L27=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL27" s="8">
+      <c r="AL27" s="7">
         <f>IF(M27=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM27" s="8">
+      <c r="AM27" s="7">
         <f>IF(N27=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN27" s="8">
+      <c r="AN27" s="7">
         <f>IF(O27=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO27" s="8">
+      <c r="AO27" s="7">
         <f>IF(P27=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP27" s="8">
+      <c r="AP27" s="7">
         <f>IF(Q27=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ27" s="8">
+      <c r="AQ27" s="7">
         <f>IF(R27=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR27" s="8">
+      <c r="AR27" s="7">
         <f>IF(S27=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS27" s="8">
+      <c r="AS27" s="7">
         <f>IF(T27=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT27" s="8">
+      <c r="AT27" s="7">
         <f>IF(U27=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU27" s="8">
+      <c r="AU27" s="7">
         <f>IF(V27=V$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV27" s="8">
+      <c r="AV27" s="7">
         <f>IF(W27=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW27" s="8">
+      <c r="AW27" s="7">
         <f>IF(X27=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX27" s="8">
+      <c r="AX27" s="7">
         <f>IF(Y27=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY27" s="8">
+      <c r="AY27" s="7">
         <f>IF(Z27=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ27" s="8">
+      <c r="AZ27" s="7">
         <f>IF(AA27=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA27" s="8">
+      <c r="BA27" s="7">
         <f>IF(AB27=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB27" s="8">
+      <c r="BB27" s="7">
         <f>IF(AC27=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC27" s="8">
+      <c r="BC27" s="7">
         <f>IF(AD27=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD27" s="8">
+      <c r="BD27" s="7">
         <f>IF(AE27=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE27" s="8">
+      <c r="BE27" s="7">
         <f>IF(AF27=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF27" s="8">
+      <c r="BF27" s="7">
         <f>SUM(AG27:BE27)*4</f>
         <v>84</v>
       </c>
@@ -9083,107 +9090,107 @@
       <c r="AF28" s="4">
         <v>3</v>
       </c>
-      <c r="AG28" s="8">
+      <c r="AG28" s="7">
         <f>IF(H28=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH28" s="8">
+      <c r="AH28" s="7">
         <f>IF(I28=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI28" s="8">
+      <c r="AI28" s="7">
         <f>IF(J28=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ28" s="8">
+      <c r="AJ28" s="7">
         <f>IF(K28=K$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AK28" s="8">
+      <c r="AK28" s="7">
         <f>IF(L28=L$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AL28" s="8">
+      <c r="AL28" s="7">
         <f>IF(M28=M$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AM28" s="8">
+      <c r="AM28" s="7">
         <f>IF(N28=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN28" s="8">
+      <c r="AN28" s="7">
         <f>IF(O28=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO28" s="8">
+      <c r="AO28" s="7">
         <f>IF(P28=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP28" s="8">
+      <c r="AP28" s="7">
         <f>IF(Q28=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ28" s="8">
+      <c r="AQ28" s="7">
         <f>IF(R28=R$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR28" s="8">
+      <c r="AR28" s="7">
         <f>IF(S28=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS28" s="8">
+      <c r="AS28" s="7">
         <f>IF(T28=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT28" s="8">
+      <c r="AT28" s="7">
         <f>IF(U28=U$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU28" s="8">
+      <c r="AU28" s="7">
         <f>IF(V28=V$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AV28" s="8">
+      <c r="AV28" s="7">
         <f>IF(W28=W$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AW28" s="8">
+      <c r="AW28" s="7">
         <f>IF(X28=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX28" s="8">
+      <c r="AX28" s="7">
         <f>IF(Y28=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY28" s="8">
+      <c r="AY28" s="7">
         <f>IF(Z28=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ28" s="8">
+      <c r="AZ28" s="7">
         <f>IF(AA28=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA28" s="8">
+      <c r="BA28" s="7">
         <f>IF(AB28=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB28" s="8">
+      <c r="BB28" s="7">
         <f>IF(AC28=AC$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC28" s="8">
+      <c r="BC28" s="7">
         <f>IF(AD28=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD28" s="8">
+      <c r="BD28" s="7">
         <f>IF(AE28=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE28" s="8">
+      <c r="BE28" s="7">
         <f>IF(AF28=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF28" s="8">
+      <c r="BF28" s="7">
         <f>SUM(AG28:BE28)*4</f>
         <v>32</v>
       </c>
@@ -9285,107 +9292,107 @@
       <c r="AF29" s="4">
         <v>3</v>
       </c>
-      <c r="AG29" s="8">
+      <c r="AG29" s="7">
         <f>IF(H29=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH29" s="8">
+      <c r="AH29" s="7">
         <f>IF(I29=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI29" s="8">
+      <c r="AI29" s="7">
         <f>IF(J29=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ29" s="8">
+      <c r="AJ29" s="7">
         <f>IF(K29=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK29" s="8">
+      <c r="AK29" s="7">
         <f>IF(L29=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL29" s="8">
+      <c r="AL29" s="7">
         <f>IF(M29=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM29" s="8">
+      <c r="AM29" s="7">
         <f>IF(N29=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN29" s="8">
+      <c r="AN29" s="7">
         <f>IF(O29=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO29" s="8">
+      <c r="AO29" s="7">
         <f>IF(P29=P$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AP29" s="8">
+      <c r="AP29" s="7">
         <f>IF(Q29=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ29" s="8">
+      <c r="AQ29" s="7">
         <f>IF(R29=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR29" s="8">
+      <c r="AR29" s="7">
         <f>IF(S29=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS29" s="8">
+      <c r="AS29" s="7">
         <f>IF(T29=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT29" s="8">
+      <c r="AT29" s="7">
         <f>IF(U29=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU29" s="8">
+      <c r="AU29" s="7">
         <f>IF(V29=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV29" s="8">
+      <c r="AV29" s="7">
         <f>IF(W29=W$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AW29" s="8">
+      <c r="AW29" s="7">
         <f>IF(X29=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX29" s="8">
+      <c r="AX29" s="7">
         <f>IF(Y29=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY29" s="8">
+      <c r="AY29" s="7">
         <f>IF(Z29=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ29" s="8">
+      <c r="AZ29" s="7">
         <f>IF(AA29=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA29" s="8">
+      <c r="BA29" s="7">
         <f>IF(AB29=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB29" s="8">
+      <c r="BB29" s="7">
         <f>IF(AC29=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC29" s="8">
+      <c r="BC29" s="7">
         <f>IF(AD29=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD29" s="8">
+      <c r="BD29" s="7">
         <f>IF(AE29=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE29" s="8">
+      <c r="BE29" s="7">
         <f>IF(AF29=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF29" s="8">
+      <c r="BF29" s="7">
         <f>SUM(AG29:BE29)*4</f>
         <v>76</v>
       </c>
@@ -9487,107 +9494,107 @@
       <c r="AF30" s="4">
         <v>3</v>
       </c>
-      <c r="AG30" s="8">
+      <c r="AG30" s="7">
         <f>IF(H30=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH30" s="8">
+      <c r="AH30" s="7">
         <f>IF(I30=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI30" s="8">
+      <c r="AI30" s="7">
         <f>IF(J30=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ30" s="8">
+      <c r="AJ30" s="7">
         <f>IF(K30=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK30" s="8">
+      <c r="AK30" s="7">
         <f>IF(L30=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL30" s="8">
+      <c r="AL30" s="7">
         <f>IF(M30=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM30" s="8">
+      <c r="AM30" s="7">
         <f>IF(N30=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN30" s="8">
+      <c r="AN30" s="7">
         <f>IF(O30=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO30" s="8">
+      <c r="AO30" s="7">
         <f>IF(P30=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP30" s="8">
+      <c r="AP30" s="7">
         <f>IF(Q30=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ30" s="8">
+      <c r="AQ30" s="7">
         <f>IF(R30=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR30" s="8">
+      <c r="AR30" s="7">
         <f>IF(S30=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS30" s="8">
+      <c r="AS30" s="7">
         <f>IF(T30=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT30" s="8">
+      <c r="AT30" s="7">
         <f>IF(U30=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU30" s="8">
+      <c r="AU30" s="7">
         <f>IF(V30=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV30" s="8">
+      <c r="AV30" s="7">
         <f>IF(W30=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW30" s="8">
+      <c r="AW30" s="7">
         <f>IF(X30=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX30" s="8">
+      <c r="AX30" s="7">
         <f>IF(Y30=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY30" s="8">
+      <c r="AY30" s="7">
         <f>IF(Z30=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ30" s="8">
+      <c r="AZ30" s="7">
         <f>IF(AA30=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA30" s="8">
+      <c r="BA30" s="7">
         <f>IF(AB30=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB30" s="8">
+      <c r="BB30" s="7">
         <f>IF(AC30=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC30" s="8">
+      <c r="BC30" s="7">
         <f>IF(AD30=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD30" s="8">
+      <c r="BD30" s="7">
         <f>IF(AE30=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE30" s="8">
+      <c r="BE30" s="7">
         <f>IF(AF30=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF30" s="8">
+      <c r="BF30" s="7">
         <f>SUM(AG30:BE30)*4</f>
         <v>100</v>
       </c>
@@ -9689,107 +9696,107 @@
       <c r="AF31" s="4">
         <v>3</v>
       </c>
-      <c r="AG31" s="8">
+      <c r="AG31" s="7">
         <f>IF(H31=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH31" s="8">
+      <c r="AH31" s="7">
         <f>IF(I31=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI31" s="8">
+      <c r="AI31" s="7">
         <f>IF(J31=J$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AJ31" s="8">
+      <c r="AJ31" s="7">
         <f>IF(K31=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK31" s="8">
+      <c r="AK31" s="7">
         <f>IF(L31=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL31" s="8">
+      <c r="AL31" s="7">
         <f>IF(M31=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM31" s="8">
+      <c r="AM31" s="7">
         <f>IF(N31=N$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AN31" s="8">
+      <c r="AN31" s="7">
         <f>IF(O31=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO31" s="8">
+      <c r="AO31" s="7">
         <f>IF(P31=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP31" s="8">
+      <c r="AP31" s="7">
         <f>IF(Q31=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ31" s="8">
+      <c r="AQ31" s="7">
         <f>IF(R31=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR31" s="8">
+      <c r="AR31" s="7">
         <f>IF(S31=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS31" s="8">
+      <c r="AS31" s="7">
         <f>IF(T31=T$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT31" s="8">
+      <c r="AT31" s="7">
         <f>IF(U31=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU31" s="8">
+      <c r="AU31" s="7">
         <f>IF(V31=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV31" s="8">
+      <c r="AV31" s="7">
         <f>IF(W31=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW31" s="8">
+      <c r="AW31" s="7">
         <f>IF(X31=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX31" s="8">
+      <c r="AX31" s="7">
         <f>IF(Y31=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY31" s="8">
+      <c r="AY31" s="7">
         <f>IF(Z31=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ31" s="8">
+      <c r="AZ31" s="7">
         <f>IF(AA31=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA31" s="8">
+      <c r="BA31" s="7">
         <f>IF(AB31=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB31" s="8">
+      <c r="BB31" s="7">
         <f>IF(AC31=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC31" s="8">
+      <c r="BC31" s="7">
         <f>IF(AD31=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD31" s="8">
+      <c r="BD31" s="7">
         <f>IF(AE31=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE31" s="8">
+      <c r="BE31" s="7">
         <f>IF(AF31=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF31" s="8">
+      <c r="BF31" s="7">
         <f>SUM(AG31:BE31)*4</f>
         <v>60</v>
       </c>
@@ -9891,107 +9898,107 @@
       <c r="AF32" s="4">
         <v>2</v>
       </c>
-      <c r="AG32" s="8">
+      <c r="AG32" s="7">
         <f>IF(H32=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH32" s="8">
+      <c r="AH32" s="7">
         <f>IF(I32=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI32" s="8">
+      <c r="AI32" s="7">
         <f>IF(J32=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ32" s="8">
+      <c r="AJ32" s="7">
         <f>IF(K32=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK32" s="8">
+      <c r="AK32" s="7">
         <f>IF(L32=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL32" s="8">
+      <c r="AL32" s="7">
         <f>IF(M32=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM32" s="8">
+      <c r="AM32" s="7">
         <f>IF(N32=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN32" s="8">
+      <c r="AN32" s="7">
         <f>IF(O32=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO32" s="8">
+      <c r="AO32" s="7">
         <f>IF(P32=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP32" s="8">
+      <c r="AP32" s="7">
         <f>IF(Q32=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ32" s="8">
+      <c r="AQ32" s="7">
         <f>IF(R32=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR32" s="8">
+      <c r="AR32" s="7">
         <f>IF(S32=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS32" s="8">
+      <c r="AS32" s="7">
         <f>IF(T32=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT32" s="8">
+      <c r="AT32" s="7">
         <f>IF(U32=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU32" s="8">
+      <c r="AU32" s="7">
         <f>IF(V32=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV32" s="8">
+      <c r="AV32" s="7">
         <f>IF(W32=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW32" s="8">
+      <c r="AW32" s="7">
         <f>IF(X32=X$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AX32" s="8">
+      <c r="AX32" s="7">
         <f>IF(Y32=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY32" s="8">
+      <c r="AY32" s="7">
         <f>IF(Z32=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ32" s="8">
+      <c r="AZ32" s="7">
         <f>IF(AA32=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA32" s="8">
+      <c r="BA32" s="7">
         <f>IF(AB32=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB32" s="8">
+      <c r="BB32" s="7">
         <f>IF(AC32=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC32" s="8">
+      <c r="BC32" s="7">
         <f>IF(AD32=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD32" s="8">
+      <c r="BD32" s="7">
         <f>IF(AE32=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE32" s="8">
+      <c r="BE32" s="7">
         <f>IF(AF32=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF32" s="8">
+      <c r="BF32" s="7">
         <f>SUM(AG32:BE32)*4</f>
         <v>84</v>
       </c>
@@ -10093,107 +10100,107 @@
       <c r="AF33" s="4">
         <v>3</v>
       </c>
-      <c r="AG33" s="8">
+      <c r="AG33" s="7">
         <f>IF(H33=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH33" s="8">
+      <c r="AH33" s="7">
         <f>IF(I33=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI33" s="8">
+      <c r="AI33" s="7">
         <f>IF(J33=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ33" s="8">
+      <c r="AJ33" s="7">
         <f>IF(K33=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK33" s="8">
+      <c r="AK33" s="7">
         <f>IF(L33=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL33" s="8">
+      <c r="AL33" s="7">
         <f>IF(M33=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM33" s="8">
+      <c r="AM33" s="7">
         <f>IF(N33=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN33" s="8">
+      <c r="AN33" s="7">
         <f>IF(O33=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO33" s="8">
+      <c r="AO33" s="7">
         <f>IF(P33=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP33" s="8">
+      <c r="AP33" s="7">
         <f>IF(Q33=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ33" s="8">
+      <c r="AQ33" s="7">
         <f>IF(R33=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR33" s="8">
+      <c r="AR33" s="7">
         <f>IF(S33=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS33" s="8">
+      <c r="AS33" s="7">
         <f>IF(T33=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT33" s="8">
+      <c r="AT33" s="7">
         <f>IF(U33=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU33" s="8">
+      <c r="AU33" s="7">
         <f>IF(V33=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV33" s="8">
+      <c r="AV33" s="7">
         <f>IF(W33=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW33" s="8">
+      <c r="AW33" s="7">
         <f>IF(X33=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX33" s="8">
+      <c r="AX33" s="7">
         <f>IF(Y33=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY33" s="8">
+      <c r="AY33" s="7">
         <f>IF(Z33=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ33" s="8">
+      <c r="AZ33" s="7">
         <f>IF(AA33=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA33" s="8">
+      <c r="BA33" s="7">
         <f>IF(AB33=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB33" s="8">
+      <c r="BB33" s="7">
         <f>IF(AC33=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC33" s="8">
+      <c r="BC33" s="7">
         <f>IF(AD33=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD33" s="8">
+      <c r="BD33" s="7">
         <f>IF(AE33=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE33" s="8">
+      <c r="BE33" s="7">
         <f>IF(AF33=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF33" s="8">
+      <c r="BF33" s="7">
         <f>SUM(AG33:BE33)*4</f>
         <v>100</v>
       </c>
@@ -10295,107 +10302,107 @@
       <c r="AF34" s="4">
         <v>2</v>
       </c>
-      <c r="AG34" s="8">
+      <c r="AG34" s="7">
         <f>IF(H34=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH34" s="8">
+      <c r="AH34" s="7">
         <f>IF(I34=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI34" s="8">
+      <c r="AI34" s="7">
         <f>IF(J34=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ34" s="8">
+      <c r="AJ34" s="7">
         <f>IF(K34=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK34" s="8">
+      <c r="AK34" s="7">
         <f>IF(L34=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL34" s="8">
+      <c r="AL34" s="7">
         <f>IF(M34=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM34" s="8">
+      <c r="AM34" s="7">
         <f>IF(N34=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN34" s="8">
+      <c r="AN34" s="7">
         <f>IF(O34=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO34" s="8">
+      <c r="AO34" s="7">
         <f>IF(P34=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP34" s="8">
+      <c r="AP34" s="7">
         <f>IF(Q34=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ34" s="8">
+      <c r="AQ34" s="7">
         <f>IF(R34=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR34" s="8">
+      <c r="AR34" s="7">
         <f>IF(S34=S$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS34" s="8">
+      <c r="AS34" s="7">
         <f>IF(T34=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT34" s="8">
+      <c r="AT34" s="7">
         <f>IF(U34=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU34" s="8">
+      <c r="AU34" s="7">
         <f>IF(V34=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV34" s="8">
+      <c r="AV34" s="7">
         <f>IF(W34=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW34" s="8">
+      <c r="AW34" s="7">
         <f>IF(X34=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX34" s="8">
+      <c r="AX34" s="7">
         <f>IF(Y34=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY34" s="8">
+      <c r="AY34" s="7">
         <f>IF(Z34=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ34" s="8">
+      <c r="AZ34" s="7">
         <f>IF(AA34=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA34" s="8">
+      <c r="BA34" s="7">
         <f>IF(AB34=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB34" s="8">
+      <c r="BB34" s="7">
         <f>IF(AC34=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC34" s="8">
+      <c r="BC34" s="7">
         <f>IF(AD34=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD34" s="8">
+      <c r="BD34" s="7">
         <f>IF(AE34=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE34" s="8">
+      <c r="BE34" s="7">
         <f>IF(AF34=AF$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BF34" s="8">
+      <c r="BF34" s="7">
         <f>SUM(AG34:BE34)*4</f>
         <v>84</v>
       </c>
@@ -10497,107 +10504,107 @@
       <c r="AF35" s="4">
         <v>3</v>
       </c>
-      <c r="AG35" s="8">
+      <c r="AG35" s="7">
         <f>IF(H35=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH35" s="8">
+      <c r="AH35" s="7">
         <f>IF(I35=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI35" s="8">
+      <c r="AI35" s="7">
         <f>IF(J35=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ35" s="8">
+      <c r="AJ35" s="7">
         <f>IF(K35=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK35" s="8">
+      <c r="AK35" s="7">
         <f>IF(L35=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL35" s="8">
+      <c r="AL35" s="7">
         <f>IF(M35=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM35" s="8">
+      <c r="AM35" s="7">
         <f>IF(N35=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN35" s="8">
+      <c r="AN35" s="7">
         <f>IF(O35=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO35" s="8">
+      <c r="AO35" s="7">
         <f>IF(P35=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP35" s="8">
+      <c r="AP35" s="7">
         <f>IF(Q35=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ35" s="8">
+      <c r="AQ35" s="7">
         <f>IF(R35=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR35" s="8">
+      <c r="AR35" s="7">
         <f>IF(S35=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS35" s="8">
+      <c r="AS35" s="7">
         <f>IF(T35=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT35" s="8">
+      <c r="AT35" s="7">
         <f>IF(U35=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU35" s="8">
+      <c r="AU35" s="7">
         <f>IF(V35=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV35" s="8">
+      <c r="AV35" s="7">
         <f>IF(W35=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW35" s="8">
+      <c r="AW35" s="7">
         <f>IF(X35=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX35" s="8">
+      <c r="AX35" s="7">
         <f>IF(Y35=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY35" s="8">
+      <c r="AY35" s="7">
         <f>IF(Z35=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ35" s="8">
+      <c r="AZ35" s="7">
         <f>IF(AA35=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA35" s="8">
+      <c r="BA35" s="7">
         <f>IF(AB35=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB35" s="8">
+      <c r="BB35" s="7">
         <f>IF(AC35=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC35" s="8">
+      <c r="BC35" s="7">
         <f>IF(AD35=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD35" s="8">
+      <c r="BD35" s="7">
         <f>IF(AE35=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE35" s="8">
+      <c r="BE35" s="7">
         <f>IF(AF35=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF35" s="8">
+      <c r="BF35" s="7">
         <f>SUM(AG35:BE35)*4</f>
         <v>96</v>
       </c>
@@ -10699,107 +10706,107 @@
       <c r="AF36" s="4">
         <v>3</v>
       </c>
-      <c r="AG36" s="8">
+      <c r="AG36" s="7">
         <f>IF(H36=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH36" s="8">
+      <c r="AH36" s="7">
         <f>IF(I36=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI36" s="8">
+      <c r="AI36" s="7">
         <f>IF(J36=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ36" s="8">
+      <c r="AJ36" s="7">
         <f>IF(K36=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK36" s="8">
+      <c r="AK36" s="7">
         <f>IF(L36=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL36" s="8">
+      <c r="AL36" s="7">
         <f>IF(M36=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM36" s="8">
+      <c r="AM36" s="7">
         <f>IF(N36=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN36" s="8">
+      <c r="AN36" s="7">
         <f>IF(O36=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO36" s="8">
+      <c r="AO36" s="7">
         <f>IF(P36=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP36" s="8">
+      <c r="AP36" s="7">
         <f>IF(Q36=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ36" s="8">
+      <c r="AQ36" s="7">
         <f>IF(R36=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR36" s="8">
+      <c r="AR36" s="7">
         <f>IF(S36=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS36" s="8">
+      <c r="AS36" s="7">
         <f>IF(T36=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT36" s="8">
+      <c r="AT36" s="7">
         <f>IF(U36=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU36" s="8">
+      <c r="AU36" s="7">
         <f>IF(V36=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV36" s="8">
+      <c r="AV36" s="7">
         <f>IF(W36=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW36" s="8">
+      <c r="AW36" s="7">
         <f>IF(X36=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX36" s="8">
+      <c r="AX36" s="7">
         <f>IF(Y36=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY36" s="8">
+      <c r="AY36" s="7">
         <f>IF(Z36=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ36" s="8">
+      <c r="AZ36" s="7">
         <f>IF(AA36=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA36" s="8">
+      <c r="BA36" s="7">
         <f>IF(AB36=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB36" s="8">
+      <c r="BB36" s="7">
         <f>IF(AC36=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC36" s="8">
+      <c r="BC36" s="7">
         <f>IF(AD36=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD36" s="8">
+      <c r="BD36" s="7">
         <f>IF(AE36=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE36" s="8">
+      <c r="BE36" s="7">
         <f>IF(AF36=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF36" s="8">
+      <c r="BF36" s="7">
         <f>SUM(AG36:BE36)*4</f>
         <v>100</v>
       </c>
@@ -10901,107 +10908,107 @@
       <c r="AF37" s="4">
         <v>3</v>
       </c>
-      <c r="AG37" s="8">
+      <c r="AG37" s="7">
         <f>IF(H37=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH37" s="8">
+      <c r="AH37" s="7">
         <f>IF(I37=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI37" s="8">
+      <c r="AI37" s="7">
         <f>IF(J37=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ37" s="8">
+      <c r="AJ37" s="7">
         <f>IF(K37=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK37" s="8">
+      <c r="AK37" s="7">
         <f>IF(L37=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL37" s="8">
+      <c r="AL37" s="7">
         <f>IF(M37=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM37" s="8">
+      <c r="AM37" s="7">
         <f>IF(N37=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN37" s="8">
+      <c r="AN37" s="7">
         <f>IF(O37=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO37" s="8">
+      <c r="AO37" s="7">
         <f>IF(P37=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP37" s="8">
+      <c r="AP37" s="7">
         <f>IF(Q37=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ37" s="8">
+      <c r="AQ37" s="7">
         <f>IF(R37=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR37" s="8">
+      <c r="AR37" s="7">
         <f>IF(S37=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS37" s="8">
+      <c r="AS37" s="7">
         <f>IF(T37=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT37" s="8">
+      <c r="AT37" s="7">
         <f>IF(U37=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU37" s="8">
+      <c r="AU37" s="7">
         <f>IF(V37=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV37" s="8">
+      <c r="AV37" s="7">
         <f>IF(W37=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW37" s="8">
+      <c r="AW37" s="7">
         <f>IF(X37=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX37" s="8">
+      <c r="AX37" s="7">
         <f>IF(Y37=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY37" s="8">
+      <c r="AY37" s="7">
         <f>IF(Z37=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ37" s="8">
+      <c r="AZ37" s="7">
         <f>IF(AA37=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA37" s="8">
+      <c r="BA37" s="7">
         <f>IF(AB37=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB37" s="8">
+      <c r="BB37" s="7">
         <f>IF(AC37=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC37" s="8">
+      <c r="BC37" s="7">
         <f>IF(AD37=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD37" s="8">
+      <c r="BD37" s="7">
         <f>IF(AE37=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE37" s="8">
+      <c r="BE37" s="7">
         <f>IF(AF37=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF37" s="8">
+      <c r="BF37" s="7">
         <f>SUM(AG37:BE37)*4</f>
         <v>100</v>
       </c>
@@ -11103,107 +11110,107 @@
       <c r="AF38" s="4">
         <v>3</v>
       </c>
-      <c r="AG38" s="8">
+      <c r="AG38" s="7">
         <f>IF(H38=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH38" s="8">
+      <c r="AH38" s="7">
         <f>IF(I38=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI38" s="8">
+      <c r="AI38" s="7">
         <f>IF(J38=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ38" s="8">
+      <c r="AJ38" s="7">
         <f>IF(K38=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK38" s="8">
+      <c r="AK38" s="7">
         <f>IF(L38=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL38" s="8">
+      <c r="AL38" s="7">
         <f>IF(M38=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM38" s="8">
+      <c r="AM38" s="7">
         <f>IF(N38=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN38" s="8">
+      <c r="AN38" s="7">
         <f>IF(O38=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO38" s="8">
+      <c r="AO38" s="7">
         <f>IF(P38=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP38" s="8">
+      <c r="AP38" s="7">
         <f>IF(Q38=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ38" s="8">
+      <c r="AQ38" s="7">
         <f>IF(R38=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR38" s="8">
+      <c r="AR38" s="7">
         <f>IF(S38=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS38" s="8">
+      <c r="AS38" s="7">
         <f>IF(T38=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT38" s="8">
+      <c r="AT38" s="7">
         <f>IF(U38=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU38" s="8">
+      <c r="AU38" s="7">
         <f>IF(V38=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV38" s="8">
+      <c r="AV38" s="7">
         <f>IF(W38=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW38" s="8">
+      <c r="AW38" s="7">
         <f>IF(X38=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX38" s="8">
+      <c r="AX38" s="7">
         <f>IF(Y38=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY38" s="8">
+      <c r="AY38" s="7">
         <f>IF(Z38=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ38" s="8">
+      <c r="AZ38" s="7">
         <f>IF(AA38=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA38" s="8">
+      <c r="BA38" s="7">
         <f>IF(AB38=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB38" s="8">
+      <c r="BB38" s="7">
         <f>IF(AC38=AC$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BC38" s="8">
+      <c r="BC38" s="7">
         <f>IF(AD38=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD38" s="8">
+      <c r="BD38" s="7">
         <f>IF(AE38=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE38" s="8">
+      <c r="BE38" s="7">
         <f>IF(AF38=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF38" s="8">
+      <c r="BF38" s="7">
         <f>SUM(AG38:BE38)*4</f>
         <v>96</v>
       </c>
@@ -11305,107 +11312,107 @@
       <c r="AF39" s="4">
         <v>3</v>
       </c>
-      <c r="AG39" s="8">
+      <c r="AG39" s="7">
         <f>IF(H39=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH39" s="8">
+      <c r="AH39" s="7">
         <f>IF(I39=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI39" s="8">
+      <c r="AI39" s="7">
         <f>IF(J39=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ39" s="8">
+      <c r="AJ39" s="7">
         <f>IF(K39=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK39" s="8">
+      <c r="AK39" s="7">
         <f>IF(L39=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL39" s="8">
+      <c r="AL39" s="7">
         <f>IF(M39=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM39" s="8">
+      <c r="AM39" s="7">
         <f>IF(N39=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN39" s="8">
+      <c r="AN39" s="7">
         <f>IF(O39=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO39" s="8">
+      <c r="AO39" s="7">
         <f>IF(P39=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP39" s="8">
+      <c r="AP39" s="7">
         <f>IF(Q39=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ39" s="8">
+      <c r="AQ39" s="7">
         <f>IF(R39=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR39" s="8">
+      <c r="AR39" s="7">
         <f>IF(S39=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS39" s="8">
+      <c r="AS39" s="7">
         <f>IF(T39=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT39" s="8">
+      <c r="AT39" s="7">
         <f>IF(U39=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU39" s="8">
+      <c r="AU39" s="7">
         <f>IF(V39=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV39" s="8">
+      <c r="AV39" s="7">
         <f>IF(W39=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW39" s="8">
+      <c r="AW39" s="7">
         <f>IF(X39=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX39" s="8">
+      <c r="AX39" s="7">
         <f>IF(Y39=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY39" s="8">
+      <c r="AY39" s="7">
         <f>IF(Z39=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ39" s="8">
+      <c r="AZ39" s="7">
         <f>IF(AA39=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA39" s="8">
+      <c r="BA39" s="7">
         <f>IF(AB39=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB39" s="8">
+      <c r="BB39" s="7">
         <f>IF(AC39=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC39" s="8">
+      <c r="BC39" s="7">
         <f>IF(AD39=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD39" s="8">
+      <c r="BD39" s="7">
         <f>IF(AE39=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE39" s="8">
+      <c r="BE39" s="7">
         <f>IF(AF39=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF39" s="8">
+      <c r="BF39" s="7">
         <f>SUM(AG39:BE39)*4</f>
         <v>100</v>
       </c>
@@ -11507,107 +11514,107 @@
       <c r="AF40" s="4">
         <v>3</v>
       </c>
-      <c r="AG40" s="8">
+      <c r="AG40" s="7">
         <f>IF(H40=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH40" s="8">
+      <c r="AH40" s="7">
         <f>IF(I40=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI40" s="8">
+      <c r="AI40" s="7">
         <f>IF(J40=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ40" s="8">
+      <c r="AJ40" s="7">
         <f>IF(K40=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK40" s="8">
+      <c r="AK40" s="7">
         <f>IF(L40=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL40" s="8">
+      <c r="AL40" s="7">
         <f>IF(M40=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM40" s="8">
+      <c r="AM40" s="7">
         <f>IF(N40=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN40" s="8">
+      <c r="AN40" s="7">
         <f>IF(O40=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO40" s="8">
+      <c r="AO40" s="7">
         <f>IF(P40=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP40" s="8">
+      <c r="AP40" s="7">
         <f>IF(Q40=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ40" s="8">
+      <c r="AQ40" s="7">
         <f>IF(R40=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR40" s="8">
+      <c r="AR40" s="7">
         <f>IF(S40=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS40" s="8">
+      <c r="AS40" s="7">
         <f>IF(T40=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT40" s="8">
+      <c r="AT40" s="7">
         <f>IF(U40=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU40" s="8">
+      <c r="AU40" s="7">
         <f>IF(V40=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV40" s="8">
+      <c r="AV40" s="7">
         <f>IF(W40=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW40" s="8">
+      <c r="AW40" s="7">
         <f>IF(X40=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX40" s="8">
+      <c r="AX40" s="7">
         <f>IF(Y40=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY40" s="8">
+      <c r="AY40" s="7">
         <f>IF(Z40=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ40" s="8">
+      <c r="AZ40" s="7">
         <f>IF(AA40=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA40" s="8">
+      <c r="BA40" s="7">
         <f>IF(AB40=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB40" s="8">
+      <c r="BB40" s="7">
         <f>IF(AC40=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC40" s="8">
+      <c r="BC40" s="7">
         <f>IF(AD40=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD40" s="8">
+      <c r="BD40" s="7">
         <f>IF(AE40=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE40" s="8">
+      <c r="BE40" s="7">
         <f>IF(AF40=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF40" s="8">
+      <c r="BF40" s="7">
         <f>SUM(AG40:BE40)*4</f>
         <v>92</v>
       </c>
@@ -11709,107 +11716,107 @@
       <c r="AF41" s="4">
         <v>3</v>
       </c>
-      <c r="AG41" s="8">
+      <c r="AG41" s="7">
         <f>IF(H41=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH41" s="8">
+      <c r="AH41" s="7">
         <f>IF(I41=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI41" s="8">
+      <c r="AI41" s="7">
         <f>IF(J41=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ41" s="8">
+      <c r="AJ41" s="7">
         <f>IF(K41=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK41" s="8">
+      <c r="AK41" s="7">
         <f>IF(L41=L$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AL41" s="8">
+      <c r="AL41" s="7">
         <f>IF(M41=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM41" s="8">
+      <c r="AM41" s="7">
         <f>IF(N41=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN41" s="8">
+      <c r="AN41" s="7">
         <f>IF(O41=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO41" s="8">
+      <c r="AO41" s="7">
         <f>IF(P41=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP41" s="8">
+      <c r="AP41" s="7">
         <f>IF(Q41=Q$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AQ41" s="8">
+      <c r="AQ41" s="7">
         <f>IF(R41=R$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AR41" s="8">
+      <c r="AR41" s="7">
         <f>IF(S41=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS41" s="8">
+      <c r="AS41" s="7">
         <f>IF(T41=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT41" s="8">
+      <c r="AT41" s="7">
         <f>IF(U41=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU41" s="8">
+      <c r="AU41" s="7">
         <f>IF(V41=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV41" s="8">
+      <c r="AV41" s="7">
         <f>IF(W41=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW41" s="8">
+      <c r="AW41" s="7">
         <f>IF(X41=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX41" s="8">
+      <c r="AX41" s="7">
         <f>IF(Y41=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY41" s="8">
+      <c r="AY41" s="7">
         <f>IF(Z41=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ41" s="8">
+      <c r="AZ41" s="7">
         <f>IF(AA41=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA41" s="8">
+      <c r="BA41" s="7">
         <f>IF(AB41=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB41" s="8">
+      <c r="BB41" s="7">
         <f>IF(AC41=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC41" s="8">
+      <c r="BC41" s="7">
         <f>IF(AD41=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD41" s="8">
+      <c r="BD41" s="7">
         <f>IF(AE41=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE41" s="8">
+      <c r="BE41" s="7">
         <f>IF(AF41=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF41" s="8">
+      <c r="BF41" s="7">
         <f>SUM(AG41:BE41)*4</f>
         <v>76</v>
       </c>
@@ -11911,107 +11918,107 @@
       <c r="AF42" s="4">
         <v>3</v>
       </c>
-      <c r="AG42" s="8">
+      <c r="AG42" s="7">
         <f>IF(H42=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH42" s="8">
+      <c r="AH42" s="7">
         <f>IF(I42=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI42" s="8">
+      <c r="AI42" s="7">
         <f>IF(J42=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ42" s="8">
+      <c r="AJ42" s="7">
         <f>IF(K42=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK42" s="8">
+      <c r="AK42" s="7">
         <f>IF(L42=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL42" s="8">
+      <c r="AL42" s="7">
         <f>IF(M42=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM42" s="8">
+      <c r="AM42" s="7">
         <f>IF(N42=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN42" s="8">
+      <c r="AN42" s="7">
         <f>IF(O42=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO42" s="8">
+      <c r="AO42" s="7">
         <f>IF(P42=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP42" s="8">
+      <c r="AP42" s="7">
         <f>IF(Q42=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ42" s="8">
+      <c r="AQ42" s="7">
         <f>IF(R42=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR42" s="8">
+      <c r="AR42" s="7">
         <f>IF(S42=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS42" s="8">
+      <c r="AS42" s="7">
         <f>IF(T42=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT42" s="8">
+      <c r="AT42" s="7">
         <f>IF(U42=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU42" s="8">
+      <c r="AU42" s="7">
         <f>IF(V42=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV42" s="8">
+      <c r="AV42" s="7">
         <f>IF(W42=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW42" s="8">
+      <c r="AW42" s="7">
         <f>IF(X42=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX42" s="8">
+      <c r="AX42" s="7">
         <f>IF(Y42=Y$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AY42" s="8">
+      <c r="AY42" s="7">
         <f>IF(Z42=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ42" s="8">
+      <c r="AZ42" s="7">
         <f>IF(AA42=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA42" s="8">
+      <c r="BA42" s="7">
         <f>IF(AB42=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB42" s="8">
+      <c r="BB42" s="7">
         <f>IF(AC42=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC42" s="8">
+      <c r="BC42" s="7">
         <f>IF(AD42=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD42" s="8">
+      <c r="BD42" s="7">
         <f>IF(AE42=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE42" s="8">
+      <c r="BE42" s="7">
         <f>IF(AF42=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF42" s="8">
+      <c r="BF42" s="7">
         <f>SUM(AG42:BE42)*4</f>
         <v>96</v>
       </c>
@@ -12113,107 +12120,107 @@
       <c r="AF43" s="4">
         <v>3</v>
       </c>
-      <c r="AG43" s="8">
+      <c r="AG43" s="7">
         <f>IF(H43=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH43" s="8">
+      <c r="AH43" s="7">
         <f>IF(I43=I$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AI43" s="8">
+      <c r="AI43" s="7">
         <f>IF(J43=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ43" s="8">
+      <c r="AJ43" s="7">
         <f>IF(K43=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK43" s="8">
+      <c r="AK43" s="7">
         <f>IF(L43=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL43" s="8">
+      <c r="AL43" s="7">
         <f>IF(M43=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM43" s="8">
+      <c r="AM43" s="7">
         <f>IF(N43=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN43" s="8">
+      <c r="AN43" s="7">
         <f>IF(O43=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO43" s="8">
+      <c r="AO43" s="7">
         <f>IF(P43=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP43" s="8">
+      <c r="AP43" s="7">
         <f>IF(Q43=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ43" s="8">
+      <c r="AQ43" s="7">
         <f>IF(R43=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR43" s="8">
+      <c r="AR43" s="7">
         <f>IF(S43=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS43" s="8">
+      <c r="AS43" s="7">
         <f>IF(T43=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT43" s="8">
+      <c r="AT43" s="7">
         <f>IF(U43=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU43" s="8">
+      <c r="AU43" s="7">
         <f>IF(V43=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV43" s="8">
+      <c r="AV43" s="7">
         <f>IF(W43=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW43" s="8">
+      <c r="AW43" s="7">
         <f>IF(X43=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX43" s="8">
+      <c r="AX43" s="7">
         <f>IF(Y43=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY43" s="8">
+      <c r="AY43" s="7">
         <f>IF(Z43=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ43" s="8">
+      <c r="AZ43" s="7">
         <f>IF(AA43=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA43" s="8">
+      <c r="BA43" s="7">
         <f>IF(AB43=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB43" s="8">
+      <c r="BB43" s="7">
         <f>IF(AC43=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC43" s="8">
+      <c r="BC43" s="7">
         <f>IF(AD43=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD43" s="8">
+      <c r="BD43" s="7">
         <f>IF(AE43=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE43" s="8">
+      <c r="BE43" s="7">
         <f>IF(AF43=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF43" s="8">
+      <c r="BF43" s="7">
         <f>SUM(AG43:BE43)*4</f>
         <v>92</v>
       </c>
@@ -12315,107 +12322,107 @@
       <c r="AF44" s="4">
         <v>3</v>
       </c>
-      <c r="AG44" s="8">
+      <c r="AG44" s="7">
         <f>IF(H44=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH44" s="8">
+      <c r="AH44" s="7">
         <f>IF(I44=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI44" s="8">
+      <c r="AI44" s="7">
         <f>IF(J44=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ44" s="8">
+      <c r="AJ44" s="7">
         <f>IF(K44=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK44" s="8">
+      <c r="AK44" s="7">
         <f>IF(L44=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL44" s="8">
+      <c r="AL44" s="7">
         <f>IF(M44=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM44" s="8">
+      <c r="AM44" s="7">
         <f>IF(N44=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN44" s="8">
+      <c r="AN44" s="7">
         <f>IF(O44=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO44" s="8">
+      <c r="AO44" s="7">
         <f>IF(P44=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP44" s="8">
+      <c r="AP44" s="7">
         <f>IF(Q44=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ44" s="8">
+      <c r="AQ44" s="7">
         <f>IF(R44=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR44" s="8">
+      <c r="AR44" s="7">
         <f>IF(S44=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS44" s="8">
+      <c r="AS44" s="7">
         <f>IF(T44=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT44" s="8">
+      <c r="AT44" s="7">
         <f>IF(U44=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU44" s="8">
+      <c r="AU44" s="7">
         <f>IF(V44=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV44" s="8">
+      <c r="AV44" s="7">
         <f>IF(W44=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW44" s="8">
+      <c r="AW44" s="7">
         <f>IF(X44=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX44" s="8">
+      <c r="AX44" s="7">
         <f>IF(Y44=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY44" s="8">
+      <c r="AY44" s="7">
         <f>IF(Z44=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ44" s="8">
+      <c r="AZ44" s="7">
         <f>IF(AA44=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA44" s="8">
+      <c r="BA44" s="7">
         <f>IF(AB44=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB44" s="8">
+      <c r="BB44" s="7">
         <f>IF(AC44=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC44" s="8">
+      <c r="BC44" s="7">
         <f>IF(AD44=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD44" s="8">
+      <c r="BD44" s="7">
         <f>IF(AE44=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE44" s="8">
+      <c r="BE44" s="7">
         <f>IF(AF44=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF44" s="8">
+      <c r="BF44" s="7">
         <f>SUM(AG44:BE44)*4</f>
         <v>100</v>
       </c>
@@ -12517,107 +12524,107 @@
       <c r="AF45" s="4">
         <v>3</v>
       </c>
-      <c r="AG45" s="8">
+      <c r="AG45" s="7">
         <f>IF(H45=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH45" s="8">
+      <c r="AH45" s="7">
         <f>IF(I45=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI45" s="8">
+      <c r="AI45" s="7">
         <f>IF(J45=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ45" s="8">
+      <c r="AJ45" s="7">
         <f>IF(K45=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK45" s="8">
+      <c r="AK45" s="7">
         <f>IF(L45=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL45" s="8">
+      <c r="AL45" s="7">
         <f>IF(M45=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM45" s="8">
+      <c r="AM45" s="7">
         <f>IF(N45=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN45" s="8">
+      <c r="AN45" s="7">
         <f>IF(O45=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO45" s="8">
+      <c r="AO45" s="7">
         <f>IF(P45=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP45" s="8">
+      <c r="AP45" s="7">
         <f>IF(Q45=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ45" s="8">
+      <c r="AQ45" s="7">
         <f>IF(R45=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR45" s="8">
+      <c r="AR45" s="7">
         <f>IF(S45=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS45" s="8">
+      <c r="AS45" s="7">
         <f>IF(T45=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT45" s="8">
+      <c r="AT45" s="7">
         <f>IF(U45=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU45" s="8">
+      <c r="AU45" s="7">
         <f>IF(V45=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV45" s="8">
+      <c r="AV45" s="7">
         <f>IF(W45=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW45" s="8">
+      <c r="AW45" s="7">
         <f>IF(X45=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX45" s="8">
+      <c r="AX45" s="7">
         <f>IF(Y45=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY45" s="8">
+      <c r="AY45" s="7">
         <f>IF(Z45=Z$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AZ45" s="8">
+      <c r="AZ45" s="7">
         <f>IF(AA45=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA45" s="8">
+      <c r="BA45" s="7">
         <f>IF(AB45=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB45" s="8">
+      <c r="BB45" s="7">
         <f>IF(AC45=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC45" s="8">
+      <c r="BC45" s="7">
         <f>IF(AD45=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD45" s="8">
+      <c r="BD45" s="7">
         <f>IF(AE45=AE$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BE45" s="8">
+      <c r="BE45" s="7">
         <f>IF(AF45=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF45" s="8">
+      <c r="BF45" s="7">
         <f>SUM(AG45:BE45)*4</f>
         <v>92</v>
       </c>
@@ -12719,107 +12726,107 @@
       <c r="AF46" s="4">
         <v>3</v>
       </c>
-      <c r="AG46" s="8">
+      <c r="AG46" s="7">
         <f>IF(H46=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH46" s="8">
+      <c r="AH46" s="7">
         <f>IF(I46=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI46" s="8">
+      <c r="AI46" s="7">
         <f>IF(J46=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ46" s="8">
+      <c r="AJ46" s="7">
         <f>IF(K46=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK46" s="8">
+      <c r="AK46" s="7">
         <f>IF(L46=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL46" s="8">
+      <c r="AL46" s="7">
         <f>IF(M46=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM46" s="8">
+      <c r="AM46" s="7">
         <f>IF(N46=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN46" s="8">
+      <c r="AN46" s="7">
         <f>IF(O46=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO46" s="8">
+      <c r="AO46" s="7">
         <f>IF(P46=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP46" s="8">
+      <c r="AP46" s="7">
         <f>IF(Q46=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ46" s="8">
+      <c r="AQ46" s="7">
         <f>IF(R46=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR46" s="8">
+      <c r="AR46" s="7">
         <f>IF(S46=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS46" s="8">
+      <c r="AS46" s="7">
         <f>IF(T46=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT46" s="8">
+      <c r="AT46" s="7">
         <f>IF(U46=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU46" s="8">
+      <c r="AU46" s="7">
         <f>IF(V46=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV46" s="8">
+      <c r="AV46" s="7">
         <f>IF(W46=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW46" s="8">
+      <c r="AW46" s="7">
         <f>IF(X46=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX46" s="8">
+      <c r="AX46" s="7">
         <f>IF(Y46=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY46" s="8">
+      <c r="AY46" s="7">
         <f>IF(Z46=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ46" s="8">
+      <c r="AZ46" s="7">
         <f>IF(AA46=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA46" s="8">
+      <c r="BA46" s="7">
         <f>IF(AB46=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB46" s="8">
+      <c r="BB46" s="7">
         <f>IF(AC46=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC46" s="8">
+      <c r="BC46" s="7">
         <f>IF(AD46=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD46" s="8">
+      <c r="BD46" s="7">
         <f>IF(AE46=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE46" s="8">
+      <c r="BE46" s="7">
         <f>IF(AF46=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF46" s="8">
+      <c r="BF46" s="7">
         <f>SUM(AG46:BE46)*4</f>
         <v>100</v>
       </c>
@@ -12921,107 +12928,107 @@
       <c r="AF47" s="4">
         <v>3</v>
       </c>
-      <c r="AG47" s="8">
+      <c r="AG47" s="7">
         <f>IF(H47=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH47" s="8">
+      <c r="AH47" s="7">
         <f>IF(I47=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI47" s="8">
+      <c r="AI47" s="7">
         <f>IF(J47=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ47" s="8">
+      <c r="AJ47" s="7">
         <f>IF(K47=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK47" s="8">
+      <c r="AK47" s="7">
         <f>IF(L47=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL47" s="8">
+      <c r="AL47" s="7">
         <f>IF(M47=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM47" s="8">
+      <c r="AM47" s="7">
         <f>IF(N47=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN47" s="8">
+      <c r="AN47" s="7">
         <f>IF(O47=O$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AO47" s="8">
+      <c r="AO47" s="7">
         <f>IF(P47=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP47" s="8">
+      <c r="AP47" s="7">
         <f>IF(Q47=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ47" s="8">
+      <c r="AQ47" s="7">
         <f>IF(R47=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR47" s="8">
+      <c r="AR47" s="7">
         <f>IF(S47=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS47" s="8">
+      <c r="AS47" s="7">
         <f>IF(T47=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT47" s="8">
+      <c r="AT47" s="7">
         <f>IF(U47=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU47" s="8">
+      <c r="AU47" s="7">
         <f>IF(V47=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV47" s="8">
+      <c r="AV47" s="7">
         <f>IF(W47=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW47" s="8">
+      <c r="AW47" s="7">
         <f>IF(X47=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX47" s="8">
+      <c r="AX47" s="7">
         <f>IF(Y47=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY47" s="8">
+      <c r="AY47" s="7">
         <f>IF(Z47=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ47" s="8">
+      <c r="AZ47" s="7">
         <f>IF(AA47=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA47" s="8">
+      <c r="BA47" s="7">
         <f>IF(AB47=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB47" s="8">
+      <c r="BB47" s="7">
         <f>IF(AC47=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC47" s="8">
+      <c r="BC47" s="7">
         <f>IF(AD47=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD47" s="8">
+      <c r="BD47" s="7">
         <f>IF(AE47=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE47" s="8">
+      <c r="BE47" s="7">
         <f>IF(AF47=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF47" s="8">
+      <c r="BF47" s="7">
         <f>SUM(AG47:BE47)*4</f>
         <v>96</v>
       </c>
@@ -13123,107 +13130,107 @@
       <c r="AF48" s="4">
         <v>3</v>
       </c>
-      <c r="AG48" s="8">
+      <c r="AG48" s="7">
         <f>IF(H48=H$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="AH48" s="8">
+      <c r="AH48" s="7">
         <f>IF(I48=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI48" s="8">
+      <c r="AI48" s="7">
         <f>IF(J48=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ48" s="8">
+      <c r="AJ48" s="7">
         <f>IF(K48=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK48" s="8">
+      <c r="AK48" s="7">
         <f>IF(L48=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL48" s="8">
+      <c r="AL48" s="7">
         <f>IF(M48=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM48" s="8">
+      <c r="AM48" s="7">
         <f>IF(N48=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN48" s="8">
+      <c r="AN48" s="7">
         <f>IF(O48=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO48" s="8">
+      <c r="AO48" s="7">
         <f>IF(P48=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP48" s="8">
+      <c r="AP48" s="7">
         <f>IF(Q48=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ48" s="8">
+      <c r="AQ48" s="7">
         <f>IF(R48=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR48" s="8">
+      <c r="AR48" s="7">
         <f>IF(S48=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS48" s="8">
+      <c r="AS48" s="7">
         <f>IF(T48=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT48" s="8">
+      <c r="AT48" s="7">
         <f>IF(U48=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU48" s="8">
+      <c r="AU48" s="7">
         <f>IF(V48=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV48" s="8">
+      <c r="AV48" s="7">
         <f>IF(W48=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW48" s="8">
+      <c r="AW48" s="7">
         <f>IF(X48=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX48" s="8">
+      <c r="AX48" s="7">
         <f>IF(Y48=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY48" s="8">
+      <c r="AY48" s="7">
         <f>IF(Z48=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ48" s="8">
+      <c r="AZ48" s="7">
         <f>IF(AA48=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA48" s="8">
+      <c r="BA48" s="7">
         <f>IF(AB48=AB$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BB48" s="8">
+      <c r="BB48" s="7">
         <f>IF(AC48=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC48" s="8">
+      <c r="BC48" s="7">
         <f>IF(AD48=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD48" s="8">
+      <c r="BD48" s="7">
         <f>IF(AE48=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE48" s="8">
+      <c r="BE48" s="7">
         <f>IF(AF48=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF48" s="8">
+      <c r="BF48" s="7">
         <f>SUM(AG48:BE48)*4</f>
         <v>96</v>
       </c>
@@ -13325,146 +13332,146 @@
       <c r="AF49" s="4">
         <v>3</v>
       </c>
-      <c r="AG49" s="8">
+      <c r="AG49" s="7">
         <f>IF(H49=H$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AH49" s="8">
+      <c r="AH49" s="7">
         <f>IF(I49=I$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AI49" s="8">
+      <c r="AI49" s="7">
         <f>IF(J49=J$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ49" s="8">
+      <c r="AJ49" s="7">
         <f>IF(K49=K$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AK49" s="8">
+      <c r="AK49" s="7">
         <f>IF(L49=L$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AL49" s="8">
+      <c r="AL49" s="7">
         <f>IF(M49=M$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AM49" s="8">
+      <c r="AM49" s="7">
         <f>IF(N49=N$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AN49" s="8">
+      <c r="AN49" s="7">
         <f>IF(O49=O$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AO49" s="8">
+      <c r="AO49" s="7">
         <f>IF(P49=P$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AP49" s="8">
+      <c r="AP49" s="7">
         <f>IF(Q49=Q$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AQ49" s="8">
+      <c r="AQ49" s="7">
         <f>IF(R49=R$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AR49" s="8">
+      <c r="AR49" s="7">
         <f>IF(S49=S$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AS49" s="8">
+      <c r="AS49" s="7">
         <f>IF(T49=T$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AT49" s="8">
+      <c r="AT49" s="7">
         <f>IF(U49=U$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AU49" s="8">
+      <c r="AU49" s="7">
         <f>IF(V49=V$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AV49" s="8">
+      <c r="AV49" s="7">
         <f>IF(W49=W$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AW49" s="8">
+      <c r="AW49" s="7">
         <f>IF(X49=X$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AX49" s="8">
+      <c r="AX49" s="7">
         <f>IF(Y49=Y$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AY49" s="8">
+      <c r="AY49" s="7">
         <f>IF(Z49=Z$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="AZ49" s="8">
+      <c r="AZ49" s="7">
         <f>IF(AA49=AA$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA49" s="8">
+      <c r="BA49" s="7">
         <f>IF(AB49=AB$50,1,0)</f>
         <v>0</v>
       </c>
-      <c r="BB49" s="8">
+      <c r="BB49" s="7">
         <f>IF(AC49=AC$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BC49" s="8">
+      <c r="BC49" s="7">
         <f>IF(AD49=AD$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BD49" s="8">
+      <c r="BD49" s="7">
         <f>IF(AE49=AE$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BE49" s="8">
+      <c r="BE49" s="7">
         <f>IF(AF49=AF$50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="BF49" s="8">
+      <c r="BF49" s="7">
         <f>SUM(AG49:BE49)*4</f>
         <v>96</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="8:58">
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:58">
       <c r="H50" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I50" s="6" t="s">
+      <c r="I50" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J50" s="6" t="s">
+      <c r="J50" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="L50" s="6" t="s">
+      <c r="L50" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="M50" s="6" t="s">
+      <c r="M50" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="N50" s="6" t="s">
+      <c r="N50" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="O50" s="6" t="s">
+      <c r="O50" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="P50" s="6" t="s">
+      <c r="P50" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="Q50" s="6" t="s">
+      <c r="Q50" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="R50" s="6" t="s">
+      <c r="R50" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="S50" s="6" t="s">
+      <c r="S50" s="8" t="s">
         <v>105</v>
       </c>
       <c r="T50" s="4" t="s">
@@ -13510,6 +13517,72 @@
       <c r="BF50" s="9">
         <f>SUM(AG50:BE50)*4</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:58">
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
+      <c r="V51" s="10"/>
+      <c r="W51" s="10"/>
+      <c r="X51" s="10"/>
+      <c r="Y51" s="10"/>
+      <c r="Z51" s="10"/>
+      <c r="AA51" s="10"/>
+      <c r="AB51" s="10"/>
+      <c r="AC51" s="10"/>
+      <c r="AD51" s="10"/>
+      <c r="AE51" s="10"/>
+      <c r="AF51" s="10"/>
+      <c r="AG51" s="7">
+        <f>IF(H51=H$50,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH51" s="10"/>
+      <c r="AI51" s="10"/>
+      <c r="AJ51" s="10"/>
+      <c r="AK51" s="10"/>
+      <c r="AL51" s="10"/>
+      <c r="AM51" s="10"/>
+      <c r="AN51" s="10"/>
+      <c r="AO51" s="10"/>
+      <c r="AP51" s="10"/>
+      <c r="AQ51" s="10"/>
+      <c r="AR51" s="10"/>
+      <c r="AS51" s="10"/>
+      <c r="AT51" s="10"/>
+      <c r="AU51" s="10"/>
+      <c r="AV51" s="10"/>
+      <c r="AW51" s="10"/>
+      <c r="AX51" s="10"/>
+      <c r="AY51" s="10"/>
+      <c r="AZ51" s="10"/>
+      <c r="BA51" s="10"/>
+      <c r="BB51" s="10"/>
+      <c r="BC51" s="10"/>
+      <c r="BD51" s="10"/>
+      <c r="BE51" s="10"/>
+      <c r="BF51" s="7">
+        <f>AVERAGE(BF2:BF49)</f>
+        <v>82.5</v>
       </c>
     </row>
   </sheetData>
